--- a/data/trending_integrated_20260910_12.xlsx
+++ b/data/trending_integrated_20260910_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4615</v>
+        <v>4415</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+130.75%</t>
+          <t>+120.75%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="F2" t="n">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="G2" t="n">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="H2" t="n">
         <v>3.2</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>597182634152</v>
+        <v>615306098402</v>
       </c>
       <c r="P2" t="n">
         <v>5700</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>합병 대상 업종 신재생에너지 관련 기대감 속 급등. 과도한 욕심 경계.</t>
+          <t>합병 대상 업종 호재와 높은 시가총액 대비 주가 상승 기대감.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스팩', '신재생에너지', '합병']</t>
+          <t>['스팩', '합병']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,10 +670,10 @@
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F3" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G3" t="n">
         <v>42</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29500</v>
+        <v>29700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+27.16%</t>
+          <t>+28.02%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F4" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G4" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H4" t="n">
         <v>7.54</v>
@@ -794,7 +794,7 @@
         <v>7.58</v>
       </c>
       <c r="O4" t="n">
-        <v>41427629400</v>
+        <v>42213423575</v>
       </c>
       <c r="P4" t="n">
         <v>34750</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14840</v>
+        <v>14800</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+22.75%</t>
+          <t>+22.42%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -857,10 +857,10 @@
         <v>349</v>
       </c>
       <c r="F5" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G5" t="n">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="H5" t="n">
         <v>0.03</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>267589713340</v>
+        <v>270289294345</v>
       </c>
       <c r="P5" t="n">
         <v>36200</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>이란발 지정학적 리스크 고조에 따른 유가 급등 및 석유주 강세. 호르무즈 해협 관련 뉴스.</t>
+          <t>중동 긴장 고조에 따른 유가 급등 수혜 기대감과 거래량 증가.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['유가 급등', '이란', '호르무즈']</t>
+          <t>['유가', '거래량']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,70 +931,70 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>한국석유</t>
+          <t>테라뷰</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13210</v>
+        <v>3535</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+14.37%</t>
+          <t>+13.85%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.26</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F6" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G6" t="n">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="H6" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>11550</v>
+        <v>3105</v>
       </c>
       <c r="K6" t="n">
-        <v>11780</v>
+        <v>3170</v>
       </c>
       <c r="L6" t="n">
-        <v>14880</v>
+        <v>3775</v>
       </c>
       <c r="M6" t="n">
-        <v>11700</v>
+        <v>3165</v>
       </c>
       <c r="N6" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>90743442775</v>
+        <v>22802894843</v>
       </c>
       <c r="P6" t="n">
-        <v>33575</v>
+        <v>20800</v>
       </c>
       <c r="Q6" t="n">
-        <v>9690</v>
+        <v>1700</v>
       </c>
       <c r="R6" t="n">
-        <v>-78000</v>
+        <v>16000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>흥구석유와 키 맞추기 움직임 속 상한가 기록. 15% 이상 상승 및 연상 기대감 형성.</t>
+          <t>단기 과열 상태에서 목표가 상향 및 텐버거 기대감 표출. 일부 매도 의견과 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['흥구석유', '키맞추기', '연상']</t>
+          <t>['목표가', '단기과열', '주가조작']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1016,77 +1016,77 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>004090</t>
+          <t>950250</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>테라뷰</t>
+          <t>한국석유</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3545</v>
+        <v>13020</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+14.17%</t>
+          <t>+12.73%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0.26</v>
       </c>
       <c r="E7" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F7" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3105</v>
+        <v>11550</v>
       </c>
       <c r="K7" t="n">
-        <v>3170</v>
+        <v>11780</v>
       </c>
       <c r="L7" t="n">
-        <v>3775</v>
+        <v>14880</v>
       </c>
       <c r="M7" t="n">
-        <v>3165</v>
+        <v>11700</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="O7" t="n">
-        <v>22272612047</v>
+        <v>92034945150</v>
       </c>
       <c r="P7" t="n">
-        <v>20800</v>
+        <v>33575</v>
       </c>
       <c r="Q7" t="n">
-        <v>1700</v>
+        <v>9690</v>
       </c>
       <c r="R7" t="n">
-        <v>16000</v>
+        <v>-78000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>단기 과열 상태에서 목표가 상향 및 텐버거 기대감 표출. 일부 매도 의견과 주가 조작 의혹 제기.</t>
+          <t>흥구석유와 키 맞추기 움직임 속 상한가 기록. 15% 이상 상승 및 연상 기대감 형성.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['목표가', '단기과열', '주가조작']</t>
+          <t>['흥구석유', '키맞추기', '연상']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>950250</t>
+          <t>004090</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8440</v>
+        <v>8350</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+13.75%</t>
+          <t>+12.53%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>0.4</v>
       </c>
       <c r="E8" t="n">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="F8" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G8" t="n">
-        <v>1201</v>
+        <v>1235</v>
       </c>
       <c r="H8" t="n">
         <v>1.17</v>
@@ -1162,7 +1162,7 @@
         <v>0.77</v>
       </c>
       <c r="O8" t="n">
-        <v>63034219640</v>
+        <v>63456361410</v>
       </c>
       <c r="P8" t="n">
         <v>21500</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>글로벌 제약사 및 연구진 참여 폐암 신약 임상 관련 내용 기반의 긍정적 전망. 기술 이전 가능성 언급.</t>
+          <t>글로벌 제약사와의 임상 참여 및 기술 이전 기대감으로 인한 급등 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['폐암학회', '임상', '기술이전']</t>
+          <t>['임상', '기술 이전', 'FDA']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1939</v>
+        <v>1923</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+10.17%</t>
+          <t>+9.26%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F9" t="n">
         <v>67</v>
       </c>
       <c r="G9" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H9" t="n">
         <v>2.12</v>
@@ -1254,7 +1254,7 @@
         <v>2.07</v>
       </c>
       <c r="O9" t="n">
-        <v>177862304885</v>
+        <v>180984433237</v>
       </c>
       <c r="P9" t="n">
         <v>4795</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>외인 매수세 유입에도 불구하고 단기 차익 실현 매물 출회 가능성. 120일선 돌파 기대감.</t>
+          <t>외인 매수세 유입 및 주가 상승 기대감 속 단기 하락 우려.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['외인', '120일선', '차익 실현']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3930</v>
+        <v>3885</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+3.15%</t>
+          <t>+1.97%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-1.62</v>
       </c>
       <c r="E10" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F10" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G10" t="n">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="H10" t="n">
         <v>1.57</v>
@@ -1346,7 +1346,7 @@
         <v>3.19</v>
       </c>
       <c r="O10" t="n">
-        <v>128248004643</v>
+        <v>129323065114</v>
       </c>
       <c r="P10" t="n">
         <v>8100</v>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+2.56%</t>
+          <t>+1.97%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.38</v>
       </c>
       <c r="E11" t="n">
+        <v>58</v>
+      </c>
+      <c r="F11" t="n">
+        <v>27</v>
+      </c>
+      <c r="G11" t="n">
         <v>59</v>
-      </c>
-      <c r="F11" t="n">
-        <v>28</v>
-      </c>
-      <c r="G11" t="n">
-        <v>61</v>
       </c>
       <c r="H11" t="n">
         <v>2.8</v>
@@ -1438,7 +1438,7 @@
         <v>2.42</v>
       </c>
       <c r="O11" t="n">
-        <v>7781452299</v>
+        <v>7930861642</v>
       </c>
       <c r="P11" t="n">
         <v>2610</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2085</v>
+        <v>2115</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+1.44%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.34</v>
       </c>
       <c r="E12" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G12" t="n">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="H12" t="n">
         <v>0.85</v>
@@ -1530,7 +1530,7 @@
         <v>0.51</v>
       </c>
       <c r="O12" t="n">
-        <v>18416516168</v>
+        <v>18763527688</v>
       </c>
       <c r="P12" t="n">
         <v>2930</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>주요 사업 관련 소식과 함께 기타 법인 및 외국인 순매수세 유입. 주가 바닥 다지기 및 추가 상승 기대.</t>
+          <t>새만금 개발 및 LH 관련 호재 속 기관 및 기타 법인 매수세 유입.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['강동씨앤엘', '기타법인', '순매수']</t>
+          <t>['새만금', 'LH']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1853000</v>
+        <v>1854000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>795</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="G13" t="n">
-        <v>1801</v>
+        <v>1809</v>
       </c>
       <c r="H13" t="n">
         <v>50.67</v>
@@ -1622,7 +1622,7 @@
         <v>50.66</v>
       </c>
       <c r="O13" t="n">
-        <v>3261852786500</v>
+        <v>3365415952000</v>
       </c>
       <c r="P13" t="n">
         <v>2987000</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>연기금 리밸런싱 및 외국인 수급 개선에 따른 대세 상승 기대. 200만 목표.</t>
+          <t>리밸런싱 이후 폭등 기대감과 함께 단기 상승 추세 전망.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['연기금', '리밸런싱', '대세 상승']</t>
+          <t>['리밸런싱', '폭등']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14210</v>
+        <v>14220</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.77%</t>
+          <t>-0.70%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.45</v>
       </c>
       <c r="E14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G14" t="n">
-        <v>540</v>
+        <v>560</v>
       </c>
       <c r="H14" t="n">
         <v>6.09</v>
@@ -1714,7 +1714,7 @@
         <v>5.64</v>
       </c>
       <c r="O14" t="n">
-        <v>115003828755</v>
+        <v>118649555450</v>
       </c>
       <c r="P14" t="n">
         <v>30200</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>266750</v>
+        <v>267250</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.02%</t>
+          <t>-0.83%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="F15" t="n">
         <v>470</v>
       </c>
       <c r="G15" t="n">
-        <v>1288</v>
+        <v>1315</v>
       </c>
       <c r="H15" t="n">
         <v>46.81</v>
@@ -1806,7 +1806,7 @@
         <v>46.85</v>
       </c>
       <c r="O15" t="n">
-        <v>1886407886750</v>
+        <v>1946218448500</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>삼성전자 자사주 매입 리스크 부각 및 매도 의견 우세. 하이닉스와의 주가 비교.</t>
+          <t>자사주 매입 호재에도 불구하고 부정적인 전망과 매도 의견이 우세.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['자사주 매입', '매도', '리스크']</t>
+          <t>['자사주 매입']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>150800</v>
+        <v>150900</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.76%</t>
+          <t>-1.69%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.4</v>
       </c>
       <c r="E16" t="n">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="F16" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G16" t="n">
-        <v>887</v>
+        <v>899</v>
       </c>
       <c r="H16" t="n">
         <v>15.65</v>
@@ -1892,13 +1892,13 @@
         <v>164700</v>
       </c>
       <c r="M16" t="n">
-        <v>150700</v>
+        <v>150200</v>
       </c>
       <c r="N16" t="n">
         <v>15.25</v>
       </c>
       <c r="O16" t="n">
-        <v>318082874150</v>
+        <v>324474953200</v>
       </c>
       <c r="P16" t="n">
         <v>164700</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>유가 급등에 따른 수혜 기대감과 단기 차익 실현 의견 공존. JP모건 대량 매수 패턴.</t>
+          <t>유가 폭등 영향 속 주가 상승 기대감과 단기 차익 실현 의견 공존.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['유가 급등', '차익 실현', 'JP모건']</t>
+          <t>['유가', '차익 실현']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18990</v>
+        <v>19040</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.37%</t>
+          <t>-2.11%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.21</v>
       </c>
       <c r="E17" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="F17" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G17" t="n">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="H17" t="n">
         <v>10.64</v>
@@ -1990,7 +1990,7 @@
         <v>10.85</v>
       </c>
       <c r="O17" t="n">
-        <v>70443578925</v>
+        <v>72195375335</v>
       </c>
       <c r="P17" t="n">
         <v>40350</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>대규모 미국 투자 및 중동 전쟁 불확실성에도 주가 버티기. 대차 해지 운동 촉구.</t>
+          <t>대차 해지 운동 동참 독려와 함께 주가 상승 기대감 형성.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['미국 투자', '대차 해지', '중동 전쟁']</t>
+          <t>['대차 해지']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,11 +2039,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>88800</v>
+        <v>89050</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-3.16%</t>
+          <t>-2.89%</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2053,10 +2053,10 @@
         <v>214</v>
       </c>
       <c r="F18" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G18" t="n">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="H18" t="n">
         <v>23.65</v>
@@ -2082,7 +2082,7 @@
         <v>23.61</v>
       </c>
       <c r="O18" t="n">
-        <v>130720678300</v>
+        <v>133207259350</v>
       </c>
       <c r="P18" t="n">
         <v>139200</v>
@@ -2127,83 +2127,83 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14380</v>
+        <v>6620</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.88%</t>
+          <t>-3.50%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1.34</v>
+        <v>-1.03</v>
       </c>
       <c r="E19" t="n">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="F19" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="G19" t="n">
-        <v>423</v>
+        <v>278</v>
       </c>
       <c r="H19" t="n">
-        <v>2.89</v>
+        <v>15.68</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>14960</v>
+        <v>6860</v>
       </c>
       <c r="K19" t="n">
-        <v>15040</v>
+        <v>6800</v>
       </c>
       <c r="L19" t="n">
-        <v>15040</v>
+        <v>6820</v>
       </c>
       <c r="M19" t="n">
-        <v>14190</v>
+        <v>6400</v>
       </c>
       <c r="N19" t="n">
-        <v>1.55</v>
+        <v>16.71</v>
       </c>
       <c r="O19" t="n">
-        <v>75988654085</v>
+        <v>10667602825</v>
       </c>
       <c r="P19" t="n">
-        <v>31500</v>
+        <v>13000</v>
       </c>
       <c r="Q19" t="n">
-        <v>1263</v>
+        <v>6030</v>
       </c>
       <c r="R19" t="n">
-        <v>-492000</v>
+        <v>-273000</v>
       </c>
       <c r="S19" t="n">
-        <v>-7000</v>
+        <v>-10000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 광통신 관련주로서의 강세 전망 및 외인 매수세 유입 기대.</t>
+          <t>김씨일가 퇴출 요구 및 외국인 매도 지속. 로봇, 반도체 외에는 부진하며, 머시너리/서비스 분사 필요성 제기. 주가 조작 및 잡주 논란.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '외인']</t>
+          <t>['분사', '주가조작', '외국인매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,90 +2212,90 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14990</v>
+        <v>14400</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-4.16%</t>
+          <t>-3.74%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="E20" t="n">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="F20" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G20" t="n">
-        <v>333</v>
+        <v>431</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>15640</v>
+        <v>14960</v>
       </c>
       <c r="K20" t="n">
-        <v>15600</v>
+        <v>15040</v>
       </c>
       <c r="L20" t="n">
-        <v>15600</v>
+        <v>15040</v>
       </c>
       <c r="M20" t="n">
-        <v>14700</v>
+        <v>14190</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="O20" t="n">
-        <v>21368711335</v>
+        <v>77350323960</v>
       </c>
       <c r="P20" t="n">
-        <v>19380</v>
+        <v>31500</v>
       </c>
       <c r="Q20" t="n">
-        <v>3200</v>
+        <v>1263</v>
       </c>
       <c r="R20" t="n">
-        <v>1000</v>
+        <v>-492000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>최근 수주 공시 기반의 긍정적 전망 및 회복 기대감.</t>
+          <t>미국 광통신 관련주로서의 강세 전망 및 외인 매수세 유입 기대.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['수주', '공시', '반도체']</t>
+          <t>['광통신', 'AI', '외인']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>6570</v>
+        <v>15000</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-4.23%</t>
+          <t>-4.09%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-1.03</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F21" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G21" t="n">
-        <v>275</v>
+        <v>339</v>
       </c>
       <c r="H21" t="n">
-        <v>15.68</v>
+        <v>0</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,51 +2343,51 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>6860</v>
+        <v>15640</v>
       </c>
       <c r="K21" t="n">
-        <v>6800</v>
+        <v>15600</v>
       </c>
       <c r="L21" t="n">
-        <v>6820</v>
+        <v>15600</v>
       </c>
       <c r="M21" t="n">
-        <v>6400</v>
+        <v>14700</v>
       </c>
       <c r="N21" t="n">
-        <v>16.71</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>10414548200</v>
+        <v>21751998150</v>
       </c>
       <c r="P21" t="n">
-        <v>13000</v>
+        <v>19380</v>
       </c>
       <c r="Q21" t="n">
-        <v>6030</v>
+        <v>3200</v>
       </c>
       <c r="R21" t="n">
-        <v>-273000</v>
+        <v>1000</v>
       </c>
       <c r="S21" t="n">
-        <v>-10000</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>분사 이슈 및 주가 패턴에 대한 부정적 언급과 함께 로봇/반도체 분야에서의 기대감 혼재.</t>
+          <t>호남 반도체 설계 용역 발주 및 삼성 수주 가능성 언급. 킨텍스 공시 수주 확인되었으며, 역대 최대 규모의 수주 기대감 반영.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['분사', '로봇', '반도체']</t>
+          <t>['수주', '설계용역', '킨텍스']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,130 +2396,130 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3685</v>
+        <v>2140</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-4.66%</t>
+          <t>-5.31%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.54</v>
+        <v>-0.35</v>
       </c>
       <c r="E22" t="n">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="F22" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G22" t="n">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="H22" t="n">
-        <v>1.54</v>
+        <v>4.91</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>3865</v>
+        <v>2260</v>
       </c>
       <c r="K22" t="n">
-        <v>3845</v>
+        <v>2250</v>
       </c>
       <c r="L22" t="n">
-        <v>4075</v>
+        <v>2290</v>
       </c>
       <c r="M22" t="n">
-        <v>3605</v>
+        <v>2080</v>
       </c>
       <c r="N22" t="n">
-        <v>2.08</v>
+        <v>5.26</v>
       </c>
       <c r="O22" t="n">
-        <v>45755912078</v>
+        <v>5888015612</v>
       </c>
       <c r="P22" t="n">
-        <v>4335</v>
+        <v>2705</v>
       </c>
       <c r="Q22" t="n">
-        <v>1246</v>
+        <v>1418</v>
       </c>
       <c r="R22" t="n">
-        <v>-210000</v>
+        <v>-133000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>최근 하락세 속 조정 및 반등에 대한 엇갈린 전망. 일부 매수 의견과 차트 붕괴 경고.</t>
+          <t>적대적 M&amp;A 가능성 및 신규 최대주주 부각 속 주가 변동성 확대.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['조정', '나락', '분할매수']</t>
+          <t>['M&amp;A', '최대주주']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2135</v>
+        <v>29450</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-5.53%</t>
+          <t>-5.31%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.35</v>
+        <v>0.17</v>
       </c>
       <c r="E23" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="F23" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G23" t="n">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="H23" t="n">
-        <v>4.91</v>
+        <v>12.31</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,47 +2527,47 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>2260</v>
+        <v>31100</v>
       </c>
       <c r="K23" t="n">
-        <v>2250</v>
+        <v>30450</v>
       </c>
       <c r="L23" t="n">
-        <v>2290</v>
+        <v>30600</v>
       </c>
       <c r="M23" t="n">
-        <v>2080</v>
+        <v>28800</v>
       </c>
       <c r="N23" t="n">
-        <v>5.26</v>
+        <v>12.14</v>
       </c>
       <c r="O23" t="n">
-        <v>5854997672</v>
+        <v>51438833300</v>
       </c>
       <c r="P23" t="n">
-        <v>2705</v>
+        <v>75900</v>
       </c>
       <c r="Q23" t="n">
-        <v>1418</v>
+        <v>15000</v>
       </c>
       <c r="R23" t="n">
-        <v>-133000</v>
+        <v>-343000</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>적대적 M&amp;A 가능성 속 경영권 분쟁 우려. 3자 배정 유증 발표 임박.</t>
+          <t>차익실현 매물 출회 및 급락 마감. 가온전선과의 비교 속 단기 변동성 확대.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['M&amp;A', '경영권 분쟁', '유증']</t>
+          <t>['차익실현', '급락', '단기변동성']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2575,82 +2575,82 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>29350</v>
+        <v>3650</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-5.63%</t>
+          <t>-5.56%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.17</v>
+        <v>-0.54</v>
       </c>
       <c r="E24" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F24" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="G24" t="n">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="H24" t="n">
-        <v>12.31</v>
+        <v>1.54</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>31100</v>
+        <v>3865</v>
       </c>
       <c r="K24" t="n">
-        <v>30450</v>
+        <v>3845</v>
       </c>
       <c r="L24" t="n">
-        <v>30600</v>
+        <v>4075</v>
       </c>
       <c r="M24" t="n">
-        <v>28800</v>
+        <v>3605</v>
       </c>
       <c r="N24" t="n">
-        <v>12.14</v>
+        <v>2.08</v>
       </c>
       <c r="O24" t="n">
-        <v>50345057525</v>
+        <v>46392347829</v>
       </c>
       <c r="P24" t="n">
-        <v>75900</v>
+        <v>4335</v>
       </c>
       <c r="Q24" t="n">
-        <v>15000</v>
+        <v>1246</v>
       </c>
       <c r="R24" t="n">
-        <v>-343000</v>
+        <v>-210000</v>
       </c>
       <c r="S24" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>차익실현 매물 출회 및 급락 마감. 가온전선과의 비교 속 단기 변동성 확대.</t>
+          <t>최근 하락세 속 조정 및 반등에 대한 엇갈린 전망. 일부 매수 의견과 차트 붕괴 경고.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,11 +2659,11 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['차익실현', '급락', '단기변동성']</t>
+          <t>['조정', '나락', '분할매수']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
@@ -2694,13 +2694,13 @@
         <v>-0.22</v>
       </c>
       <c r="E25" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F25" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G25" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H25" t="n">
         <v>0.14</v>
@@ -2726,7 +2726,7 @@
         <v>0.36</v>
       </c>
       <c r="O25" t="n">
-        <v>60612970955</v>
+        <v>61777940250</v>
       </c>
       <c r="P25" t="n">
         <v>20850</v>
@@ -2742,16 +2742,16 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>그래핀 신소재 관련 호재 및 대규모 투자 언급과 함께 매수세 유입 관측.</t>
+          <t>창사 이래 최대 호재 및 그래핀 신소재 가능성 언급. 3500억 달러 규모의 사업과 연관된 것으로 추정되며, 개인 투자자들의 매수 대기 및 매집 정황 포착.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['그래핀', '신소재', '투자']</t>
+          <t>['그래핀', '신소재', '호재']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>28100</v>
+        <v>27900</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-7.26%</t>
+          <t>-7.92%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.02</v>
       </c>
       <c r="E26" t="n">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="F26" t="n">
         <v>98</v>
       </c>
       <c r="G26" t="n">
-        <v>331</v>
+        <v>350</v>
       </c>
       <c r="H26" t="n">
         <v>0.33</v>
@@ -2818,7 +2818,7 @@
         <v>0.31</v>
       </c>
       <c r="O26" t="n">
-        <v>113186439850</v>
+        <v>115323841950</v>
       </c>
       <c r="P26" t="n">
         <v>39350</v>
@@ -2834,16 +2834,16 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>의료기기 관련 뉴스 언급에도 불구하고 주가 하락 및 차익 실현 우려.</t>
+          <t>좋은 재료 대비 낮은 주가 상승률에 대한 불만 표출. 주포 이탈 및 계단식 하락 가능성 제기. 33000원 이상 고가 매수자들의 손실 우려.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['의료기기', '주가', '하락']</t>
+          <t>['하락', '주포이탈', '고가매수']</t>
         </is>
       </c>
       <c r="X26" t="n">
@@ -2878,13 +2878,13 @@
         <v>-0.32</v>
       </c>
       <c r="E27" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F27" t="n">
         <v>41</v>
       </c>
       <c r="G27" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="H27" t="n">
         <v>5.86</v>

--- a/data/trending_integrated_20260910_12.xlsx
+++ b/data/trending_integrated_20260910_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4415</v>
+        <v>4502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+120.75%</t>
+          <t>+125.10%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="F2" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="G2" t="n">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="H2" t="n">
         <v>3.2</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>615306098402</v>
+        <v>630011587909</v>
       </c>
       <c r="P2" t="n">
         <v>5700</v>
@@ -670,13 +670,13 @@
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F3" t="n">
         <v>37</v>
       </c>
       <c r="G3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H3" t="n">
         <v>0.07000000000000001</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29700</v>
+        <v>29400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+28.02%</t>
+          <t>+26.72%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G4" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="H4" t="n">
         <v>7.54</v>
@@ -794,7 +794,7 @@
         <v>7.58</v>
       </c>
       <c r="O4" t="n">
-        <v>42213423575</v>
+        <v>42472313975</v>
       </c>
       <c r="P4" t="n">
         <v>34750</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14800</v>
+        <v>14750</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+22.42%</t>
+          <t>+22.00%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F5" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G5" t="n">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="H5" t="n">
         <v>0.03</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>270289294345</v>
+        <v>272658642380</v>
       </c>
       <c r="P5" t="n">
         <v>36200</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>중동 긴장 고조에 따른 유가 급등 수혜 기대감과 거래량 증가.</t>
+          <t>이란발 지정학적 리스크 고조에 따른 유가 급등 수혜 기대. 트럼프 발언 및 호르무즈 해협 이슈로 인한 유가 상승 전망 강화. 단기 급등 후 차익 실현 매물 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['유가', '거래량']</t>
+          <t>['유가', '이란', '호르무즈']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3535</v>
+        <v>3545</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+13.85%</t>
+          <t>+14.17%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F6" t="n">
         <v>37</v>
       </c>
       <c r="G6" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>22802894843</v>
+        <v>22953746565</v>
       </c>
       <c r="P6" t="n">
         <v>20800</v>
@@ -1023,184 +1023,184 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>한국석유</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13020</v>
+        <v>8350</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+12.73%</t>
+          <t>+12.53%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.26</v>
+        <v>0.4</v>
       </c>
       <c r="E7" t="n">
-        <v>67</v>
+        <v>241</v>
       </c>
       <c r="F7" t="n">
-        <v>41</v>
+        <v>109</v>
       </c>
       <c r="G7" t="n">
-        <v>38</v>
+        <v>1242</v>
       </c>
       <c r="H7" t="n">
-        <v>4.37</v>
+        <v>1.17</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>11550</v>
+        <v>7420</v>
       </c>
       <c r="K7" t="n">
-        <v>11780</v>
+        <v>8000</v>
       </c>
       <c r="L7" t="n">
-        <v>14880</v>
+        <v>9100</v>
       </c>
       <c r="M7" t="n">
-        <v>11700</v>
+        <v>7930</v>
       </c>
       <c r="N7" t="n">
-        <v>4.63</v>
+        <v>0.77</v>
       </c>
       <c r="O7" t="n">
-        <v>92034945150</v>
+        <v>63708091800</v>
       </c>
       <c r="P7" t="n">
-        <v>33575</v>
+        <v>21500</v>
       </c>
       <c r="Q7" t="n">
-        <v>9690</v>
+        <v>2300</v>
       </c>
       <c r="R7" t="n">
-        <v>-78000</v>
+        <v>117000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>흥구석유와 키 맞추기 움직임 속 상한가 기록. 15% 이상 상승 및 연상 기대감 형성.</t>
+          <t>글로벌 제약사와의 임상 참여 및 기술 이전 기대감으로 인한 급등 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['흥구석유', '키맞추기', '연상']</t>
+          <t>['임상', '기술 이전', 'FDA']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>004090</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>한국석유</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8350</v>
+        <v>12950</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+12.53%</t>
+          <t>+12.12%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.4</v>
+        <v>-0.26</v>
       </c>
       <c r="E8" t="n">
-        <v>234</v>
+        <v>67</v>
       </c>
       <c r="F8" t="n">
-        <v>106</v>
+        <v>41</v>
       </c>
       <c r="G8" t="n">
-        <v>1235</v>
+        <v>40</v>
       </c>
       <c r="H8" t="n">
-        <v>1.17</v>
+        <v>4.37</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>7420</v>
+        <v>11550</v>
       </c>
       <c r="K8" t="n">
-        <v>8000</v>
+        <v>11780</v>
       </c>
       <c r="L8" t="n">
-        <v>9100</v>
+        <v>14880</v>
       </c>
       <c r="M8" t="n">
-        <v>7930</v>
+        <v>11700</v>
       </c>
       <c r="N8" t="n">
-        <v>0.77</v>
+        <v>4.63</v>
       </c>
       <c r="O8" t="n">
-        <v>63456361410</v>
+        <v>92823978395</v>
       </c>
       <c r="P8" t="n">
-        <v>21500</v>
+        <v>33575</v>
       </c>
       <c r="Q8" t="n">
-        <v>2300</v>
+        <v>9690</v>
       </c>
       <c r="R8" t="n">
-        <v>117000</v>
+        <v>-78000</v>
       </c>
       <c r="S8" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>글로벌 제약사와의 임상 참여 및 기술 이전 기대감으로 인한 급등 전망.</t>
+          <t>흥구석유와 키 맞추기 움직임 속 상한가 기록. 15% 이상 상승 및 연상 기대감 형성.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['임상', '기술 이전', 'FDA']</t>
+          <t>['흥구석유', '키맞추기', '연상']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>004090</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1923</v>
+        <v>1927</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+9.26%</t>
+          <t>+9.49%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F9" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G9" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="H9" t="n">
         <v>2.12</v>
@@ -1254,7 +1254,7 @@
         <v>2.07</v>
       </c>
       <c r="O9" t="n">
-        <v>180984433237</v>
+        <v>182087159208</v>
       </c>
       <c r="P9" t="n">
         <v>4795</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>외인 매수세 유입 및 주가 상승 기대감 속 단기 하락 우려.</t>
+          <t>외인 매수세 유입에도 불구하고 잦은 등락과 급락 반복, 주가 부양 의지에 대한 의문 제기. 120일선 돌파 기대와 함께 향후 추세에 대한 불확실성 상존.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['외인', '120일선', '주포']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>좋은사람들</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3885</v>
+        <v>515</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+1.97%</t>
+          <t>+1.38%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1.62</v>
+        <v>0.38</v>
       </c>
       <c r="E10" t="n">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="F10" t="n">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="G10" t="n">
-        <v>163</v>
+        <v>59</v>
       </c>
       <c r="H10" t="n">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,38 +1331,38 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>3810</v>
+        <v>508</v>
       </c>
       <c r="K10" t="n">
-        <v>3870</v>
+        <v>510</v>
       </c>
       <c r="L10" t="n">
-        <v>4250</v>
+        <v>585</v>
       </c>
       <c r="M10" t="n">
-        <v>3660</v>
+        <v>504</v>
       </c>
       <c r="N10" t="n">
-        <v>3.19</v>
+        <v>2.42</v>
       </c>
       <c r="O10" t="n">
-        <v>129323065114</v>
+        <v>7999097976</v>
       </c>
       <c r="P10" t="n">
-        <v>8100</v>
+        <v>2610</v>
       </c>
       <c r="Q10" t="n">
-        <v>592</v>
+        <v>255</v>
       </c>
       <c r="R10" t="n">
-        <v>-540000</v>
+        <v>-263000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>투기과열종목 지정 회피 및 6G 관련 호재로 인한 상승 기대. 장기전 대비.</t>
+          <t>액면병합 후 상승 기대와 상폐 경고가 혼재. 사실 여부 불분명한 정보 속 투자자 혼란.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['투경', '6G', '광통신']</t>
+          <t>['상폐', '병합', '감자']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>033340</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>좋은사람들</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>518</v>
+        <v>3860</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+1.97%</t>
+          <t>+1.31%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.38</v>
+        <v>-1.62</v>
       </c>
       <c r="E11" t="n">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="F11" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="G11" t="n">
-        <v>59</v>
+        <v>163</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8</v>
+        <v>1.57</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>508</v>
+        <v>3810</v>
       </c>
       <c r="K11" t="n">
-        <v>510</v>
+        <v>3870</v>
       </c>
       <c r="L11" t="n">
-        <v>585</v>
+        <v>4250</v>
       </c>
       <c r="M11" t="n">
-        <v>504</v>
+        <v>3660</v>
       </c>
       <c r="N11" t="n">
-        <v>2.42</v>
+        <v>3.19</v>
       </c>
       <c r="O11" t="n">
-        <v>7930861642</v>
+        <v>130452152218</v>
       </c>
       <c r="P11" t="n">
-        <v>2610</v>
+        <v>8100</v>
       </c>
       <c r="Q11" t="n">
-        <v>255</v>
+        <v>592</v>
       </c>
       <c r="R11" t="n">
-        <v>-263000</v>
+        <v>-540000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>액면병합 후 상승 기대와 상폐 경고가 혼재. 사실 여부 불분명한 정보 속 투자자 혼란.</t>
+          <t>투기과열종목 지정 회피 및 6G 관련 호재로 인한 상승 기대. 장기전 대비.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['상폐', '병합', '감자']</t>
+          <t>['투경', '6G', '광통신']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>033340</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2115</v>
+        <v>2110</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+1.44%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1504,7 +1504,7 @@
         <v>52</v>
       </c>
       <c r="G12" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H12" t="n">
         <v>0.85</v>
@@ -1530,7 +1530,7 @@
         <v>0.51</v>
       </c>
       <c r="O12" t="n">
-        <v>18763527688</v>
+        <v>18839666873</v>
       </c>
       <c r="P12" t="n">
         <v>2930</v>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1854000</v>
+        <v>1847000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="G13" t="n">
-        <v>1809</v>
+        <v>1849</v>
       </c>
       <c r="H13" t="n">
         <v>50.67</v>
@@ -1622,7 +1622,7 @@
         <v>50.66</v>
       </c>
       <c r="O13" t="n">
-        <v>3365415952000</v>
+        <v>3454551715500</v>
       </c>
       <c r="P13" t="n">
         <v>2987000</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>리밸런싱 이후 폭등 기대감과 함께 단기 상승 추세 전망.</t>
+          <t>연기금 리밸런싱 효과 및 외인 수급 개선에 따른 상승 추세 전망. 20만원 돌파 및 500만 주가 목표 설정. 미국 증시 흐름 연동 및 오후장 강세 전환 기대감 높음.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['리밸런싱', '폭등']</t>
+          <t>['연기금', '외인', '리밸런싱']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,83 +1667,83 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14220</v>
+        <v>267000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.70%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.45</v>
+        <v>-0.04</v>
       </c>
       <c r="E14" t="n">
-        <v>101</v>
+        <v>792</v>
       </c>
       <c r="F14" t="n">
-        <v>63</v>
+        <v>469</v>
       </c>
       <c r="G14" t="n">
-        <v>560</v>
+        <v>1307</v>
       </c>
       <c r="H14" t="n">
-        <v>6.09</v>
+        <v>46.81</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>14320</v>
+        <v>269500</v>
       </c>
       <c r="K14" t="n">
-        <v>13800</v>
+        <v>269000</v>
       </c>
       <c r="L14" t="n">
-        <v>14400</v>
+        <v>270500</v>
       </c>
       <c r="M14" t="n">
-        <v>13260</v>
+        <v>263500</v>
       </c>
       <c r="N14" t="n">
-        <v>5.64</v>
+        <v>46.85</v>
       </c>
       <c r="O14" t="n">
-        <v>118649555450</v>
+        <v>1998943404250</v>
       </c>
       <c r="P14" t="n">
-        <v>30200</v>
+        <v>374500</v>
       </c>
       <c r="Q14" t="n">
-        <v>3540</v>
+        <v>71600</v>
       </c>
       <c r="R14" t="n">
-        <v>-132000</v>
+        <v>376000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-400000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 신규 원전 건설 관련 수혜 기대감 및 공매도 금지 논의. 대장주 부각.</t>
+          <t>자사주 매입 호재에도 불구하고 부정적인 전망과 매도 의견이 우세.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['원전', '신규 원전', '공매도']</t>
+          <t>['자사주 매입']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>267250</v>
+        <v>151900</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.83%</t>
+          <t>-1.04%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.04</v>
+        <v>0.4</v>
       </c>
       <c r="E15" t="n">
-        <v>791</v>
+        <v>366</v>
       </c>
       <c r="F15" t="n">
-        <v>470</v>
+        <v>172</v>
       </c>
       <c r="G15" t="n">
-        <v>1315</v>
+        <v>911</v>
       </c>
       <c r="H15" t="n">
-        <v>46.81</v>
+        <v>15.65</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>269500</v>
+        <v>153500</v>
       </c>
       <c r="K15" t="n">
-        <v>269000</v>
+        <v>155500</v>
       </c>
       <c r="L15" t="n">
-        <v>270500</v>
+        <v>164700</v>
       </c>
       <c r="M15" t="n">
-        <v>263500</v>
+        <v>150200</v>
       </c>
       <c r="N15" t="n">
-        <v>46.85</v>
+        <v>15.25</v>
       </c>
       <c r="O15" t="n">
-        <v>1946218448500</v>
+        <v>328217619400</v>
       </c>
       <c r="P15" t="n">
-        <v>374500</v>
+        <v>164700</v>
       </c>
       <c r="Q15" t="n">
-        <v>71600</v>
+        <v>87700</v>
       </c>
       <c r="R15" t="n">
-        <v>376000</v>
+        <v>104000</v>
       </c>
       <c r="S15" t="n">
-        <v>-400000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>자사주 매입 호재에도 불구하고 부정적인 전망과 매도 의견이 우세.</t>
+          <t>유가 폭등 영향 속 주가 상승 기대감과 단기 차익 실현 의견 공존.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['자사주 매입']</t>
+          <t>['유가', '차익 실현']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>103</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>150900</v>
+        <v>14060</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.69%</t>
+          <t>-1.82%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="E16" t="n">
-        <v>359</v>
+        <v>100</v>
       </c>
       <c r="F16" t="n">
-        <v>168</v>
+        <v>62</v>
       </c>
       <c r="G16" t="n">
-        <v>899</v>
+        <v>573</v>
       </c>
       <c r="H16" t="n">
-        <v>15.65</v>
+        <v>6.09</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>153500</v>
+        <v>14320</v>
       </c>
       <c r="K16" t="n">
-        <v>155500</v>
+        <v>13800</v>
       </c>
       <c r="L16" t="n">
-        <v>164700</v>
+        <v>14400</v>
       </c>
       <c r="M16" t="n">
-        <v>150200</v>
+        <v>13260</v>
       </c>
       <c r="N16" t="n">
-        <v>15.25</v>
+        <v>5.64</v>
       </c>
       <c r="O16" t="n">
-        <v>324474953200</v>
+        <v>121592905980</v>
       </c>
       <c r="P16" t="n">
-        <v>164700</v>
+        <v>30200</v>
       </c>
       <c r="Q16" t="n">
-        <v>87700</v>
+        <v>3540</v>
       </c>
       <c r="R16" t="n">
-        <v>104000</v>
+        <v>-132000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>유가 폭등 영향 속 주가 상승 기대감과 단기 차익 실현 의견 공존.</t>
+          <t>원전주로서 미국 신규 원전 건설 이슈와 연계된 상승 기대감. 공매도 금지 및 세력 개입 가능성 언급. 단기 급등 후 조정 및 관망세 혼재.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['유가', '차익 실현']</t>
+          <t>['원전', '공매도', '세력']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19040</v>
+        <v>19020</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.11%</t>
+          <t>-2.21%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.21</v>
       </c>
       <c r="E17" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F17" t="n">
         <v>61</v>
       </c>
       <c r="G17" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="H17" t="n">
         <v>10.64</v>
@@ -1990,7 +1990,7 @@
         <v>10.85</v>
       </c>
       <c r="O17" t="n">
-        <v>72195375335</v>
+        <v>73298526540</v>
       </c>
       <c r="P17" t="n">
         <v>40350</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>대차 해지 운동 동참 독려와 함께 주가 상승 기대감 형성.</t>
+          <t>미국 투자 관련 기대감 속에서 주가 상승 전망 제시. 다만, 주주들의 대차해지 동참 요구가 반복되며 주가 부양을 위한 주주 행동 촉구. 실제 팩트 기반 분석은 부족.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['대차 해지']</t>
+          <t>['미국 투자', '대차해지', '원전']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2035,31 +2035,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>89050</v>
+        <v>6670</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>-2.77%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.04</v>
+        <v>-1.03</v>
       </c>
       <c r="E18" t="n">
-        <v>214</v>
+        <v>97</v>
       </c>
       <c r="F18" t="n">
-        <v>138</v>
+        <v>57</v>
       </c>
       <c r="G18" t="n">
-        <v>753</v>
+        <v>288</v>
       </c>
       <c r="H18" t="n">
-        <v>23.65</v>
+        <v>15.68</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>91700</v>
+        <v>6860</v>
       </c>
       <c r="K18" t="n">
-        <v>90000</v>
+        <v>6800</v>
       </c>
       <c r="L18" t="n">
-        <v>90700</v>
+        <v>6820</v>
       </c>
       <c r="M18" t="n">
-        <v>87800</v>
+        <v>6400</v>
       </c>
       <c r="N18" t="n">
-        <v>23.61</v>
+        <v>16.71</v>
       </c>
       <c r="O18" t="n">
-        <v>133207259350</v>
+        <v>11033287060</v>
       </c>
       <c r="P18" t="n">
-        <v>139200</v>
+        <v>13000</v>
       </c>
       <c r="Q18" t="n">
-        <v>57000</v>
+        <v>6030</v>
       </c>
       <c r="R18" t="n">
         <v>-273000</v>
       </c>
       <c r="S18" t="n">
-        <v>31000</v>
+        <v>-10000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 원전 건설 '팀코리아' 및 웨스턴하우스 지분 인수 가능성, 역사적 호재 언급.</t>
+          <t>분사 이슈 및 로봇/반도체 관련 기대감에도 불구하고 주가 부진. 외인 매도세 지속 및 잡주 이미지 부각. 주가 조작 및 경영진 교체 요구 등 부정적 여론 형성.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['원전', '웨스턴하우스', '호재']</t>
+          <t>['분사', '로봇', '반도체']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6620</v>
+        <v>88900</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.50%</t>
+          <t>-3.05%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-1.03</v>
+        <v>0.04</v>
       </c>
       <c r="E19" t="n">
-        <v>98</v>
+        <v>217</v>
       </c>
       <c r="F19" t="n">
-        <v>57</v>
+        <v>140</v>
       </c>
       <c r="G19" t="n">
-        <v>278</v>
+        <v>754</v>
       </c>
       <c r="H19" t="n">
-        <v>15.68</v>
+        <v>23.65</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,51 +2159,51 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>6860</v>
+        <v>91700</v>
       </c>
       <c r="K19" t="n">
-        <v>6800</v>
+        <v>90000</v>
       </c>
       <c r="L19" t="n">
-        <v>6820</v>
+        <v>90700</v>
       </c>
       <c r="M19" t="n">
-        <v>6400</v>
+        <v>87800</v>
       </c>
       <c r="N19" t="n">
-        <v>16.71</v>
+        <v>23.61</v>
       </c>
       <c r="O19" t="n">
-        <v>10667602825</v>
+        <v>135060065150</v>
       </c>
       <c r="P19" t="n">
-        <v>13000</v>
+        <v>139200</v>
       </c>
       <c r="Q19" t="n">
-        <v>6030</v>
+        <v>57000</v>
       </c>
       <c r="R19" t="n">
         <v>-273000</v>
       </c>
       <c r="S19" t="n">
-        <v>-10000</v>
+        <v>31000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>김씨일가 퇴출 요구 및 외국인 매도 지속. 로봇, 반도체 외에는 부진하며, 머시너리/서비스 분사 필요성 제기. 주가 조작 및 잡주 논란.</t>
+          <t>미국 원전 건설 '팀코리아' 및 웨스턴하우스 지분 인수 가능성, 역사적 호재 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['분사', '주가조작', '외국인매도']</t>
+          <t>['원전', '웨스턴하우스', '호재']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -2234,13 +2234,13 @@
         <v>1.34</v>
       </c>
       <c r="E20" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F20" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G20" t="n">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="H20" t="n">
         <v>2.89</v>
@@ -2266,7 +2266,7 @@
         <v>1.55</v>
       </c>
       <c r="O20" t="n">
-        <v>77350323960</v>
+        <v>78093288450</v>
       </c>
       <c r="P20" t="n">
         <v>31500</v>
@@ -2282,12 +2282,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 광통신 관련주로서의 강세 전망 및 외인 매수세 유입 기대.</t>
+          <t>미국 광통신 및 AI 관련주 동반 강세에 따른 상승 추세 전망. 외인 매수세 유입 및 120일선 돌파 시도. 16000원 돌파 및 5만원까지 목표가 제시.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2326,13 +2326,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F21" t="n">
         <v>64</v>
       </c>
       <c r="G21" t="n">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2358,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>21751998150</v>
+        <v>22181984090</v>
       </c>
       <c r="P21" t="n">
         <v>19380</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>호남 반도체 설계 용역 발주 및 삼성 수주 가능성 언급. 킨텍스 공시 수주 확인되었으며, 역대 최대 규모의 수주 기대감 반영.</t>
+          <t>킨텍스 공시 수주 및 호남 반도체 설계 용역 발주 관련 긍정적 뉴스 기반 상승 기대. 수주 잔고 증가 및 흑자 전환 전망. 14000원대 지지선 및 분할 매수 기회 제시.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['수주', '설계용역', '킨텍스']</t>
+          <t>['수주', '공시', '반도체']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2403,103 +2403,103 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2140</v>
+        <v>3670</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-5.31%</t>
+          <t>-5.05%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.35</v>
+        <v>-0.54</v>
       </c>
       <c r="E22" t="n">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="F22" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G22" t="n">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H22" t="n">
-        <v>4.91</v>
+        <v>1.54</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>2260</v>
+        <v>3865</v>
       </c>
       <c r="K22" t="n">
-        <v>2250</v>
+        <v>3845</v>
       </c>
       <c r="L22" t="n">
-        <v>2290</v>
+        <v>4075</v>
       </c>
       <c r="M22" t="n">
-        <v>2080</v>
+        <v>3605</v>
       </c>
       <c r="N22" t="n">
-        <v>5.26</v>
+        <v>2.08</v>
       </c>
       <c r="O22" t="n">
-        <v>5888015612</v>
+        <v>46724612363</v>
       </c>
       <c r="P22" t="n">
-        <v>2705</v>
+        <v>4335</v>
       </c>
       <c r="Q22" t="n">
-        <v>1418</v>
+        <v>1246</v>
       </c>
       <c r="R22" t="n">
-        <v>-133000</v>
+        <v>-210000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>적대적 M&amp;A 가능성 및 신규 최대주주 부각 속 주가 변동성 확대.</t>
+          <t>최근 하락세 속 조정 및 반등에 대한 엇갈린 전망. 일부 매수 의견과 차트 붕괴 경고.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['M&amp;A', '최대주주']</t>
+          <t>['조정', '나락', '분할매수']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>29450</v>
+        <v>2140</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2507,19 +2507,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.17</v>
+        <v>-0.35</v>
       </c>
       <c r="E23" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="F23" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G23" t="n">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="H23" t="n">
-        <v>12.31</v>
+        <v>4.91</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,47 +2527,47 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>31100</v>
+        <v>2260</v>
       </c>
       <c r="K23" t="n">
-        <v>30450</v>
+        <v>2250</v>
       </c>
       <c r="L23" t="n">
-        <v>30600</v>
+        <v>2290</v>
       </c>
       <c r="M23" t="n">
-        <v>28800</v>
+        <v>2080</v>
       </c>
       <c r="N23" t="n">
-        <v>12.14</v>
+        <v>5.26</v>
       </c>
       <c r="O23" t="n">
-        <v>51438833300</v>
+        <v>5926399687</v>
       </c>
       <c r="P23" t="n">
-        <v>75900</v>
+        <v>2705</v>
       </c>
       <c r="Q23" t="n">
-        <v>15000</v>
+        <v>1418</v>
       </c>
       <c r="R23" t="n">
-        <v>-343000</v>
+        <v>-133000</v>
       </c>
       <c r="S23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>차익실현 매물 출회 및 급락 마감. 가온전선과의 비교 속 단기 변동성 확대.</t>
+          <t>M&amp;A 관련 이슈와 신규 최대주주 등장 가능성 속에서 주가 변동성 확대. 1만원 돌파 기대감과 동시에 하한가 예상 등 상반된 전망 혼재. 유증 및 적대적 M&amp;A 관련 논쟁 지속.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['차익실현', '급락', '단기변동성']</t>
+          <t>['M&amp;A', '최대주주', '유증']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2575,82 +2575,82 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3650</v>
+        <v>29450</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-5.56%</t>
+          <t>-5.31%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.54</v>
+        <v>0.17</v>
       </c>
       <c r="E24" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="F24" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="G24" t="n">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="H24" t="n">
-        <v>1.54</v>
+        <v>12.31</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>3865</v>
+        <v>31100</v>
       </c>
       <c r="K24" t="n">
-        <v>3845</v>
+        <v>30450</v>
       </c>
       <c r="L24" t="n">
-        <v>4075</v>
+        <v>30600</v>
       </c>
       <c r="M24" t="n">
-        <v>3605</v>
+        <v>28800</v>
       </c>
       <c r="N24" t="n">
-        <v>2.08</v>
+        <v>12.14</v>
       </c>
       <c r="O24" t="n">
-        <v>46392347829</v>
+        <v>51996413825</v>
       </c>
       <c r="P24" t="n">
-        <v>4335</v>
+        <v>75900</v>
       </c>
       <c r="Q24" t="n">
-        <v>1246</v>
+        <v>15000</v>
       </c>
       <c r="R24" t="n">
-        <v>-210000</v>
+        <v>-343000</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>최근 하락세 속 조정 및 반등에 대한 엇갈린 전망. 일부 매수 의견과 차트 붕괴 경고.</t>
+          <t>차익실현 매물 출회 및 급락 마감. 가온전선과의 비교 속 단기 변동성 확대.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,11 +2659,11 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['조정', '나락', '분할매수']</t>
+          <t>['차익실현', '급락', '단기변동성']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>12100</v>
+        <v>12110</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-7.14%</t>
+          <t>-7.06%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.22</v>
       </c>
       <c r="E25" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F25" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G25" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H25" t="n">
         <v>0.14</v>
@@ -2726,7 +2726,7 @@
         <v>0.36</v>
       </c>
       <c r="O25" t="n">
-        <v>61777940250</v>
+        <v>62151099600</v>
       </c>
       <c r="P25" t="n">
         <v>20850</v>
@@ -2742,16 +2742,16 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>창사 이래 최대 호재 및 그래핀 신소재 가능성 언급. 3500억 달러 규모의 사업과 연관된 것으로 추정되며, 개인 투자자들의 매수 대기 및 매집 정황 포착.</t>
+          <t>그래핀 신소재 및 대규모 대미 투자 관련 호재 언급. 외인 매집 정황 포착 및 20% 수익 만족 후 매도 의견. 주가 급등 후 차익 실현 매물 및 심리 게임 양상.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['그래핀', '신소재', '호재']</t>
+          <t>['그래핀', '대미 투자', '외인']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2775,11 +2775,11 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>27900</v>
+        <v>27950</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-7.92%</t>
+          <t>-7.76%</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -2789,10 +2789,10 @@
         <v>207</v>
       </c>
       <c r="F26" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G26" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H26" t="n">
         <v>0.33</v>
@@ -2818,7 +2818,7 @@
         <v>0.31</v>
       </c>
       <c r="O26" t="n">
-        <v>115323841950</v>
+        <v>117074752250</v>
       </c>
       <c r="P26" t="n">
         <v>39350</v>
@@ -2884,7 +2884,7 @@
         <v>41</v>
       </c>
       <c r="G27" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="H27" t="n">
         <v>5.86</v>

--- a/data/trending_integrated_20260910_12.xlsx
+++ b/data/trending_integrated_20260910_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4502</v>
+        <v>4310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+125.10%</t>
+          <t>+115.50%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F2" t="n">
         <v>192</v>
       </c>
       <c r="G2" t="n">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="H2" t="n">
         <v>3.2</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>630011587909</v>
+        <v>634602074792</v>
       </c>
       <c r="P2" t="n">
         <v>5700</v>
@@ -670,13 +670,13 @@
         <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F3" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G3" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H3" t="n">
         <v>0.07000000000000001</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29400</v>
+        <v>29200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+26.72%</t>
+          <t>+25.86%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F4" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G4" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H4" t="n">
         <v>7.54</v>
@@ -794,7 +794,7 @@
         <v>7.58</v>
       </c>
       <c r="O4" t="n">
-        <v>42472313975</v>
+        <v>42692738400</v>
       </c>
       <c r="P4" t="n">
         <v>34750</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14750</v>
+        <v>14800</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+22.00%</t>
+          <t>+22.42%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="F5" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G5" t="n">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="H5" t="n">
         <v>0.03</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>272658642380</v>
+        <v>273304218250</v>
       </c>
       <c r="P5" t="n">
         <v>36200</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>이란발 지정학적 리스크 고조에 따른 유가 급등 수혜 기대. 트럼프 발언 및 호르무즈 해협 이슈로 인한 유가 상승 전망 강화. 단기 급등 후 차익 실현 매물 가능성 언급.</t>
+          <t>이란 관련 지정학적 리스크에 따른 유가 급등세. 트럼프 행정부의 유가 용인 분석 및 단기 폭발적 상승 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['유가', '이란', '호르무즈']</t>
+          <t>['유가', '지정학적 리스크', '이란']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,21 +935,21 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3545</v>
+        <v>3540</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+14.17%</t>
+          <t>+14.01%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F6" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G6" t="n">
         <v>56</v>
@@ -978,7 +978,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>22953746565</v>
+        <v>22998708665</v>
       </c>
       <c r="P6" t="n">
         <v>20800</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8350</v>
+        <v>8410</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+12.53%</t>
+          <t>+13.34%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1044,7 +1044,7 @@
         <v>109</v>
       </c>
       <c r="G7" t="n">
-        <v>1242</v>
+        <v>1254</v>
       </c>
       <c r="H7" t="n">
         <v>1.17</v>
@@ -1070,7 +1070,7 @@
         <v>0.77</v>
       </c>
       <c r="O7" t="n">
-        <v>63708091800</v>
+        <v>63905967870</v>
       </c>
       <c r="P7" t="n">
         <v>21500</v>
@@ -1119,18 +1119,18 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12950</v>
+        <v>12920</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+12.12%</t>
+          <t>+11.86%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.26</v>
       </c>
       <c r="E8" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F8" t="n">
         <v>41</v>
@@ -1162,7 +1162,7 @@
         <v>4.63</v>
       </c>
       <c r="O8" t="n">
-        <v>92823978395</v>
+        <v>93101656125</v>
       </c>
       <c r="P8" t="n">
         <v>33575</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1927</v>
+        <v>1942</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+9.49%</t>
+          <t>+10.34%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F9" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G9" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H9" t="n">
         <v>2.12</v>
@@ -1254,7 +1254,7 @@
         <v>2.07</v>
       </c>
       <c r="O9" t="n">
-        <v>182087159208</v>
+        <v>182889478885</v>
       </c>
       <c r="P9" t="n">
         <v>4795</v>
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>좋은사람들</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>515</v>
+        <v>2125</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+1.38%</t>
+          <t>+1.92%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.38</v>
+        <v>0.34</v>
       </c>
       <c r="E10" t="n">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="F10" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="G10" t="n">
-        <v>59</v>
+        <v>207</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8</v>
+        <v>0.85</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,91 +1331,91 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>508</v>
+        <v>2085</v>
       </c>
       <c r="K10" t="n">
-        <v>510</v>
+        <v>2255</v>
       </c>
       <c r="L10" t="n">
-        <v>585</v>
+        <v>2395</v>
       </c>
       <c r="M10" t="n">
-        <v>504</v>
+        <v>2040</v>
       </c>
       <c r="N10" t="n">
-        <v>2.42</v>
+        <v>0.51</v>
       </c>
       <c r="O10" t="n">
-        <v>7999097976</v>
+        <v>18866124773</v>
       </c>
       <c r="P10" t="n">
-        <v>2610</v>
+        <v>2930</v>
       </c>
       <c r="Q10" t="n">
-        <v>255</v>
+        <v>910</v>
       </c>
       <c r="R10" t="n">
-        <v>-263000</v>
+        <v>-175000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>액면병합 후 상승 기대와 상폐 경고가 혼재. 사실 여부 불분명한 정보 속 투자자 혼란.</t>
+          <t>새만금 개발 및 LH 관련 호재 속 기관 및 기타 법인 매수세 유입.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['상폐', '병합', '감자']</t>
+          <t>['새만금', 'LH']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>033340</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>좋은사람들</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3860</v>
+        <v>516</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+1.31%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-1.62</v>
+        <v>0.38</v>
       </c>
       <c r="E11" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="F11" t="n">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="G11" t="n">
-        <v>163</v>
+        <v>61</v>
       </c>
       <c r="H11" t="n">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>3810</v>
+        <v>508</v>
       </c>
       <c r="K11" t="n">
-        <v>3870</v>
+        <v>510</v>
       </c>
       <c r="L11" t="n">
-        <v>4250</v>
+        <v>585</v>
       </c>
       <c r="M11" t="n">
-        <v>3660</v>
+        <v>504</v>
       </c>
       <c r="N11" t="n">
-        <v>3.19</v>
+        <v>2.42</v>
       </c>
       <c r="O11" t="n">
-        <v>130452152218</v>
+        <v>8018423998</v>
       </c>
       <c r="P11" t="n">
-        <v>8100</v>
+        <v>2610</v>
       </c>
       <c r="Q11" t="n">
-        <v>592</v>
+        <v>255</v>
       </c>
       <c r="R11" t="n">
-        <v>-540000</v>
+        <v>-263000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>투기과열종목 지정 회피 및 6G 관련 호재로 인한 상승 기대. 장기전 대비.</t>
+          <t>액면병합 후 상승 기대와 상폐 경고가 혼재. 사실 여부 불분명한 정보 속 투자자 혼란.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['투경', '6G', '광통신']</t>
+          <t>['상폐', '병합', '감자']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>033340</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2110</v>
+        <v>3860</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+1.31%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.34</v>
+        <v>-1.62</v>
       </c>
       <c r="E12" t="n">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="F12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G12" t="n">
-        <v>205</v>
+        <v>161</v>
       </c>
       <c r="H12" t="n">
-        <v>0.85</v>
+        <v>1.57</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,47 +1515,47 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>2085</v>
+        <v>3810</v>
       </c>
       <c r="K12" t="n">
-        <v>2255</v>
+        <v>3870</v>
       </c>
       <c r="L12" t="n">
-        <v>2395</v>
+        <v>4250</v>
       </c>
       <c r="M12" t="n">
-        <v>2040</v>
+        <v>3660</v>
       </c>
       <c r="N12" t="n">
-        <v>0.51</v>
+        <v>3.19</v>
       </c>
       <c r="O12" t="n">
-        <v>18839666873</v>
+        <v>131505871944</v>
       </c>
       <c r="P12" t="n">
-        <v>2930</v>
+        <v>8100</v>
       </c>
       <c r="Q12" t="n">
-        <v>910</v>
+        <v>592</v>
       </c>
       <c r="R12" t="n">
-        <v>-175000</v>
+        <v>-540000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>새만금 개발 및 LH 관련 호재 속 기관 및 기타 법인 매수세 유입.</t>
+          <t>투기과열종목 지정 회피 및 5G/6G 관련 신규 수주 기대감. 주포의 흔들기에 따른 단기 변동성 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['새만금', 'LH']</t>
+          <t>['투경', '신규 수주', '5G']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1847000</v>
+        <v>1848000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.48%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="G13" t="n">
-        <v>1849</v>
+        <v>1870</v>
       </c>
       <c r="H13" t="n">
         <v>50.67</v>
@@ -1622,7 +1622,7 @@
         <v>50.66</v>
       </c>
       <c r="O13" t="n">
-        <v>3454551715500</v>
+        <v>3484080667000</v>
       </c>
       <c r="P13" t="n">
         <v>2987000</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>연기금 리밸런싱 효과 및 외인 수급 개선에 따른 상승 추세 전망. 20만원 돌파 및 500만 주가 목표 설정. 미국 증시 흐름 연동 및 오후장 강세 전환 기대감 높음.</t>
+          <t>30만원 재돌파 기대감 및 연기금 리밸런싱 흐름 분석. 외국인 매도세 관찰.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['연기금', '외인', '리밸런싱']</t>
+          <t>['반도체', '외국인']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1667,31 +1667,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>267000</v>
+        <v>152100</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>-0.91%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.04</v>
+        <v>0.4</v>
       </c>
       <c r="E14" t="n">
-        <v>792</v>
+        <v>366</v>
       </c>
       <c r="F14" t="n">
-        <v>469</v>
+        <v>171</v>
       </c>
       <c r="G14" t="n">
-        <v>1307</v>
+        <v>916</v>
       </c>
       <c r="H14" t="n">
-        <v>46.81</v>
+        <v>15.65</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>269500</v>
+        <v>153500</v>
       </c>
       <c r="K14" t="n">
-        <v>269000</v>
+        <v>155500</v>
       </c>
       <c r="L14" t="n">
-        <v>270500</v>
+        <v>164700</v>
       </c>
       <c r="M14" t="n">
-        <v>263500</v>
+        <v>150200</v>
       </c>
       <c r="N14" t="n">
-        <v>46.85</v>
+        <v>15.25</v>
       </c>
       <c r="O14" t="n">
-        <v>1998943404250</v>
+        <v>329206458650</v>
       </c>
       <c r="P14" t="n">
-        <v>374500</v>
+        <v>164700</v>
       </c>
       <c r="Q14" t="n">
-        <v>71600</v>
+        <v>87700</v>
       </c>
       <c r="R14" t="n">
-        <v>376000</v>
+        <v>104000</v>
       </c>
       <c r="S14" t="n">
-        <v>-400000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>자사주 매입 호재에도 불구하고 부정적인 전망과 매도 의견이 우세.</t>
+          <t>유가 급등에 따른 기대감 속 일부 투자자들의 이익 실현 및 관망세. 외국인 대량 매집 패턴 분석.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['자사주 매입']</t>
+          <t>['유가', '외국인']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>103</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>151900</v>
+        <v>267000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.04%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.4</v>
+        <v>-0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>366</v>
+        <v>791</v>
       </c>
       <c r="F15" t="n">
-        <v>172</v>
+        <v>468</v>
       </c>
       <c r="G15" t="n">
-        <v>911</v>
+        <v>1289</v>
       </c>
       <c r="H15" t="n">
-        <v>15.65</v>
+        <v>46.81</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>153500</v>
+        <v>269500</v>
       </c>
       <c r="K15" t="n">
-        <v>155500</v>
+        <v>269000</v>
       </c>
       <c r="L15" t="n">
-        <v>164700</v>
+        <v>270500</v>
       </c>
       <c r="M15" t="n">
-        <v>150200</v>
+        <v>263500</v>
       </c>
       <c r="N15" t="n">
-        <v>15.25</v>
+        <v>46.85</v>
       </c>
       <c r="O15" t="n">
-        <v>328217619400</v>
+        <v>2033732782250</v>
       </c>
       <c r="P15" t="n">
-        <v>164700</v>
+        <v>374500</v>
       </c>
       <c r="Q15" t="n">
-        <v>87700</v>
+        <v>71600</v>
       </c>
       <c r="R15" t="n">
-        <v>104000</v>
+        <v>376000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-400000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>유가 폭등 영향 속 주가 상승 기대감과 단기 차익 실현 의견 공존.</t>
+          <t>자사주 매입 호재에도 불구하고 부정적인 전망과 매도 의견이 우세.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['유가', '차익 실현']</t>
+          <t>['자사주 매입']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14060</v>
+        <v>14030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>-2.03%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.45</v>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F16" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G16" t="n">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="H16" t="n">
         <v>6.09</v>
@@ -1898,7 +1898,7 @@
         <v>5.64</v>
       </c>
       <c r="O16" t="n">
-        <v>121592905980</v>
+        <v>122739266155</v>
       </c>
       <c r="P16" t="n">
         <v>30200</v>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19020</v>
+        <v>19000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.21%</t>
+          <t>-2.31%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.21</v>
       </c>
       <c r="E17" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F17" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G17" t="n">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="H17" t="n">
         <v>10.64</v>
@@ -1990,7 +1990,7 @@
         <v>10.85</v>
       </c>
       <c r="O17" t="n">
-        <v>73298526540</v>
+        <v>73794863120</v>
       </c>
       <c r="P17" t="n">
         <v>40350</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6670</v>
+        <v>6690</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.77%</t>
+          <t>-2.48%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-1.03</v>
       </c>
       <c r="E18" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F18" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G18" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H18" t="n">
         <v>15.68</v>
@@ -2082,7 +2082,7 @@
         <v>16.71</v>
       </c>
       <c r="O18" t="n">
-        <v>11033287060</v>
+        <v>11095964050</v>
       </c>
       <c r="P18" t="n">
         <v>13000</v>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>분사 이슈 및 로봇/반도체 관련 기대감에도 불구하고 주가 부진. 외인 매도세 지속 및 잡주 이미지 부각. 주가 조작 및 경영진 교체 요구 등 부정적 여론 형성.</t>
+          <t>외국인 매도세 및 분사 관련 불확실성 속 기관의 관망세. 주가 조작 및 패턴 반복에 대한 불만 제기.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['분사', '로봇', '반도체']</t>
+          <t>['외국인', '기관', '분사']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>88900</v>
+        <v>89000</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.05%</t>
+          <t>-2.94%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.04</v>
       </c>
       <c r="E19" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="F19" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G19" t="n">
-        <v>754</v>
+        <v>767</v>
       </c>
       <c r="H19" t="n">
         <v>23.65</v>
@@ -2174,7 +2174,7 @@
         <v>23.61</v>
       </c>
       <c r="O19" t="n">
-        <v>135060065150</v>
+        <v>135483280550</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14400</v>
+        <v>14380</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.74%</t>
+          <t>-3.88%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>1.34</v>
       </c>
       <c r="E20" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F20" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G20" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="H20" t="n">
         <v>2.89</v>
@@ -2266,7 +2266,7 @@
         <v>1.55</v>
       </c>
       <c r="O20" t="n">
-        <v>78093288450</v>
+        <v>78532828960</v>
       </c>
       <c r="P20" t="n">
         <v>31500</v>
@@ -2315,11 +2315,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15000</v>
+        <v>14930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-4.09%</t>
+          <t>-4.54%</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2329,10 +2329,10 @@
         <v>95</v>
       </c>
       <c r="F21" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G21" t="n">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2358,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>22181984090</v>
+        <v>22357846760</v>
       </c>
       <c r="P21" t="n">
         <v>19380</v>
@@ -2403,70 +2403,70 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3670</v>
+        <v>29450</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-5.05%</t>
+          <t>-5.31%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.54</v>
+        <v>0.17</v>
       </c>
       <c r="E22" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F22" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G22" t="n">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="H22" t="n">
-        <v>1.54</v>
+        <v>12.31</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>3865</v>
+        <v>31100</v>
       </c>
       <c r="K22" t="n">
-        <v>3845</v>
+        <v>30450</v>
       </c>
       <c r="L22" t="n">
-        <v>4075</v>
+        <v>30600</v>
       </c>
       <c r="M22" t="n">
-        <v>3605</v>
+        <v>28800</v>
       </c>
       <c r="N22" t="n">
-        <v>2.08</v>
+        <v>12.14</v>
       </c>
       <c r="O22" t="n">
-        <v>46724612363</v>
+        <v>52212910675</v>
       </c>
       <c r="P22" t="n">
-        <v>4335</v>
+        <v>75900</v>
       </c>
       <c r="Q22" t="n">
-        <v>1246</v>
+        <v>15000</v>
       </c>
       <c r="R22" t="n">
-        <v>-210000</v>
+        <v>-343000</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>최근 하락세 속 조정 및 반등에 대한 엇갈린 전망. 일부 매수 의견과 차트 붕괴 경고.</t>
+          <t>차익실현 매물 출회 및 급락 마감. 가온전선과의 비교 속 단기 변동성 확대.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,11 +2475,11 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['조정', '나락', '분할매수']</t>
+          <t>['차익실현', '급락', '단기변동성']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,130 +2488,130 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2140</v>
+        <v>3645</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-5.31%</t>
+          <t>-5.69%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.35</v>
+        <v>-0.54</v>
       </c>
       <c r="E23" t="n">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="F23" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G23" t="n">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="H23" t="n">
-        <v>4.91</v>
+        <v>1.54</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>2260</v>
+        <v>3865</v>
       </c>
       <c r="K23" t="n">
-        <v>2250</v>
+        <v>3845</v>
       </c>
       <c r="L23" t="n">
-        <v>2290</v>
+        <v>4075</v>
       </c>
       <c r="M23" t="n">
-        <v>2080</v>
+        <v>3605</v>
       </c>
       <c r="N23" t="n">
-        <v>5.26</v>
+        <v>2.08</v>
       </c>
       <c r="O23" t="n">
-        <v>5926399687</v>
+        <v>46825212398</v>
       </c>
       <c r="P23" t="n">
-        <v>2705</v>
+        <v>4335</v>
       </c>
       <c r="Q23" t="n">
-        <v>1418</v>
+        <v>1246</v>
       </c>
       <c r="R23" t="n">
-        <v>-133000</v>
+        <v>-210000</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>M&amp;A 관련 이슈와 신규 최대주주 등장 가능성 속에서 주가 변동성 확대. 1만원 돌파 기대감과 동시에 하한가 예상 등 상반된 전망 혼재. 유증 및 적대적 M&amp;A 관련 논쟁 지속.</t>
+          <t>최근 하락세 속 조정 및 반등에 대한 엇갈린 전망. 일부 매수 의견과 차트 붕괴 경고.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['M&amp;A', '최대주주', '유증']</t>
+          <t>['조정', '나락', '분할매수']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>29450</v>
+        <v>2125</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-5.31%</t>
+          <t>-5.97%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.17</v>
+        <v>-0.35</v>
       </c>
       <c r="E24" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="F24" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G24" t="n">
-        <v>122</v>
+        <v>154</v>
       </c>
       <c r="H24" t="n">
-        <v>12.31</v>
+        <v>4.91</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2619,47 +2619,47 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>31100</v>
+        <v>2260</v>
       </c>
       <c r="K24" t="n">
-        <v>30450</v>
+        <v>2250</v>
       </c>
       <c r="L24" t="n">
-        <v>30600</v>
+        <v>2290</v>
       </c>
       <c r="M24" t="n">
-        <v>28800</v>
+        <v>2080</v>
       </c>
       <c r="N24" t="n">
-        <v>12.14</v>
+        <v>5.26</v>
       </c>
       <c r="O24" t="n">
-        <v>51996413825</v>
+        <v>5957115842</v>
       </c>
       <c r="P24" t="n">
-        <v>75900</v>
+        <v>2705</v>
       </c>
       <c r="Q24" t="n">
-        <v>15000</v>
+        <v>1418</v>
       </c>
       <c r="R24" t="n">
-        <v>-343000</v>
+        <v>-133000</v>
       </c>
       <c r="S24" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>차익실현 매물 출회 및 급락 마감. 가온전선과의 비교 속 단기 변동성 확대.</t>
+          <t>M&amp;A 관련 이슈와 신규 최대주주 등장 가능성 속에서 주가 변동성 확대. 1만원 돌파 기대감과 동시에 하한가 예상 등 상반된 전망 혼재. 유증 및 적대적 M&amp;A 관련 논쟁 지속.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['차익실현', '급락', '단기변동성']</t>
+          <t>['M&amp;A', '최대주주', '유증']</t>
         </is>
       </c>
       <c r="X24" t="n">
@@ -2667,12 +2667,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
@@ -2683,11 +2683,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>12110</v>
+        <v>12130</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-7.06%</t>
+          <t>-6.91%</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -2700,7 +2700,7 @@
         <v>59</v>
       </c>
       <c r="G25" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H25" t="n">
         <v>0.14</v>
@@ -2726,7 +2726,7 @@
         <v>0.36</v>
       </c>
       <c r="O25" t="n">
-        <v>62151099600</v>
+        <v>62202957350</v>
       </c>
       <c r="P25" t="n">
         <v>20850</v>
@@ -2742,16 +2742,16 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>그래핀 신소재 및 대규모 대미 투자 관련 호재 언급. 외인 매집 정황 포착 및 20% 수익 만족 후 매도 의견. 주가 급등 후 차익 실현 매물 및 심리 게임 양상.</t>
+          <t>그래핀 관련 대규모 계약 기대감 속 일부 투자자들의 이익 실현. 프로그램 매수세 관찰 및 추가 매수 대기.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['그래핀', '대미 투자', '외인']</t>
+          <t>['그래핀', '대규모 계약', '프로그램 매수']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>27950</v>
+        <v>27850</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-7.76%</t>
+          <t>-8.09%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.02</v>
       </c>
       <c r="E26" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F26" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G26" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H26" t="n">
         <v>0.33</v>
@@ -2818,7 +2818,7 @@
         <v>0.31</v>
       </c>
       <c r="O26" t="n">
-        <v>117074752250</v>
+        <v>117411839375</v>
       </c>
       <c r="P26" t="n">
         <v>39350</v>

--- a/data/trending_integrated_20260910_12.xlsx
+++ b/data/trending_integrated_20260910_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4310</v>
+        <v>4450</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+115.50%</t>
+          <t>+122.50%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="F2" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="G2" t="n">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H2" t="n">
         <v>3.2</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>634602074792</v>
+        <v>639673444784</v>
       </c>
       <c r="P2" t="n">
         <v>5700</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>합병 대상 업종 호재와 높은 시가총액 대비 주가 상승 기대감.</t>
+          <t>스팩주 합병 관련 불확실성 속에서 단기 급등 가능성 언급, 투자 주의 필요.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스팩', '합병']</t>
+          <t>['스팩주', '합병', '단기급등']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>카프로</t>
+          <t>샘표식품</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>203</v>
+        <v>29150</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+38.10%</t>
+          <t>+25.65%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="F3" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="G3" t="n">
-        <v>41</v>
+        <v>101</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07000000000000001</v>
+        <v>7.54</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>147</v>
+        <v>23200</v>
       </c>
       <c r="K3" t="n">
-        <v>181</v>
+        <v>26900</v>
       </c>
       <c r="L3" t="n">
-        <v>260</v>
+        <v>30150</v>
       </c>
       <c r="M3" t="n">
-        <v>181</v>
+        <v>24500</v>
       </c>
       <c r="N3" t="n">
-        <v>0.08</v>
+        <v>7.58</v>
       </c>
       <c r="O3" t="n">
-        <v>591170114</v>
+        <v>43468863975</v>
       </c>
       <c r="P3" t="n">
-        <v>3660</v>
+        <v>34750</v>
       </c>
       <c r="Q3" t="n">
-        <v>133</v>
+        <v>20450</v>
       </c>
       <c r="R3" t="n">
-        <v>-18000</v>
+        <v>-47000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>거래량 급증하며 60% 이상 급등. 회생 및 상장 기대감 속 추격매수 의견.</t>
+          <t>샘표식품, 샘표의 자사주 매입 및 소각 가능성과 연계된 주주환원 기대감 형성. 전체 유동주식 대비 높은 거래량 기록.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,11 +727,11 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['급등', '거래량', '회생']</t>
+          <t>['자사주', '소각', '주주환원']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,130 +740,130 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>006380</t>
+          <t>248170</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>샘표식품</t>
+          <t>흥구석유</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29200</v>
+        <v>14690</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+25.86%</t>
+          <t>+21.51%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.04</v>
+        <v>0.03</v>
       </c>
       <c r="E4" t="n">
-        <v>76</v>
+        <v>355</v>
       </c>
       <c r="F4" t="n">
-        <v>47</v>
+        <v>216</v>
       </c>
       <c r="G4" t="n">
-        <v>106</v>
+        <v>428</v>
       </c>
       <c r="H4" t="n">
-        <v>7.54</v>
+        <v>0.03</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>23200</v>
+        <v>12090</v>
       </c>
       <c r="K4" t="n">
-        <v>26900</v>
+        <v>12730</v>
       </c>
       <c r="L4" t="n">
-        <v>30150</v>
+        <v>15710</v>
       </c>
       <c r="M4" t="n">
-        <v>24500</v>
+        <v>12720</v>
       </c>
       <c r="N4" t="n">
-        <v>7.58</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>42692738400</v>
+        <v>274433757925</v>
       </c>
       <c r="P4" t="n">
-        <v>34750</v>
+        <v>36200</v>
       </c>
       <c r="Q4" t="n">
-        <v>20450</v>
+        <v>8920</v>
       </c>
       <c r="R4" t="n">
-        <v>-47000</v>
+        <v>22000</v>
       </c>
       <c r="S4" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>샘표식품, 샘표의 자사주 매입 및 소각 가능성과 연계된 주주환원 기대감 형성. 전체 유동주식 대비 높은 거래량 기록.</t>
+          <t>국제 유가 급등 및 지정학적 리스크 고조로 흥구석유 주가 급등, 추가 상승 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['자사주', '소각', '주주환원']</t>
+          <t>['국제유가', '지정학적리스크', '주가급등']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>248170</t>
+          <t>024060</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>흥구석유</t>
+          <t>테라뷰</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14800</v>
+        <v>3565</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+22.42%</t>
+          <t>+14.81%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>347</v>
+        <v>69</v>
       </c>
       <c r="F5" t="n">
-        <v>209</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>404</v>
+        <v>56</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,91 +871,91 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>12090</v>
+        <v>3105</v>
       </c>
       <c r="K5" t="n">
-        <v>12730</v>
+        <v>3170</v>
       </c>
       <c r="L5" t="n">
-        <v>15710</v>
+        <v>3775</v>
       </c>
       <c r="M5" t="n">
-        <v>12720</v>
+        <v>3165</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>273304218250</v>
+        <v>23411570765</v>
       </c>
       <c r="P5" t="n">
-        <v>36200</v>
+        <v>20800</v>
       </c>
       <c r="Q5" t="n">
-        <v>8920</v>
+        <v>1700</v>
       </c>
       <c r="R5" t="n">
-        <v>22000</v>
+        <v>16000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>이란 관련 지정학적 리스크에 따른 유가 급등세. 트럼프 행정부의 유가 용인 분석 및 단기 폭발적 상승 전망.</t>
+          <t>단기 과열 상태에서 목표가 상향 및 텐버거 기대감 표출. 일부 매도 의견과 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['유가', '지정학적 리스크', '이란']</t>
+          <t>['목표가', '단기과열', '주가조작']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>024060</t>
+          <t>950250</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>테라뷰</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3540</v>
+        <v>8340</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+14.01%</t>
+          <t>+12.40%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="E6" t="n">
-        <v>67</v>
+        <v>244</v>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>110</v>
       </c>
       <c r="G6" t="n">
-        <v>56</v>
+        <v>1283</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,183 +963,183 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3105</v>
+        <v>7420</v>
       </c>
       <c r="K6" t="n">
-        <v>3170</v>
+        <v>8000</v>
       </c>
       <c r="L6" t="n">
-        <v>3775</v>
+        <v>9100</v>
       </c>
       <c r="M6" t="n">
-        <v>3165</v>
+        <v>7930</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="O6" t="n">
-        <v>22998708665</v>
+        <v>64102836990</v>
       </c>
       <c r="P6" t="n">
-        <v>20800</v>
+        <v>21500</v>
       </c>
       <c r="Q6" t="n">
-        <v>1700</v>
+        <v>2300</v>
       </c>
       <c r="R6" t="n">
-        <v>16000</v>
+        <v>117000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>단기 과열 상태에서 목표가 상향 및 텐버거 기대감 표출. 일부 매도 의견과 주가 조작 의혹 제기.</t>
+          <t>글로벌 제약사와의 임상 참여 및 기술 이전 기대감으로 인한 급등 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['목표가', '단기과열', '주가조작']</t>
+          <t>['임상', '기술 이전', 'FDA']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>950250</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>한국석유</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8410</v>
+        <v>12920</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+13.34%</t>
+          <t>+11.86%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.4</v>
+        <v>-0.26</v>
       </c>
       <c r="E7" t="n">
-        <v>241</v>
+        <v>68</v>
       </c>
       <c r="F7" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>1254</v>
+        <v>40</v>
       </c>
       <c r="H7" t="n">
-        <v>1.17</v>
+        <v>4.37</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>7420</v>
+        <v>11550</v>
       </c>
       <c r="K7" t="n">
-        <v>8000</v>
+        <v>11780</v>
       </c>
       <c r="L7" t="n">
-        <v>9100</v>
+        <v>14880</v>
       </c>
       <c r="M7" t="n">
-        <v>7930</v>
+        <v>11700</v>
       </c>
       <c r="N7" t="n">
-        <v>0.77</v>
+        <v>4.63</v>
       </c>
       <c r="O7" t="n">
-        <v>63905967870</v>
+        <v>93430897455</v>
       </c>
       <c r="P7" t="n">
-        <v>21500</v>
+        <v>33575</v>
       </c>
       <c r="Q7" t="n">
-        <v>2300</v>
+        <v>9690</v>
       </c>
       <c r="R7" t="n">
-        <v>117000</v>
+        <v>-78000</v>
       </c>
       <c r="S7" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>글로벌 제약사와의 임상 참여 및 기술 이전 기대감으로 인한 급등 전망.</t>
+          <t>흥구석유와 키 맞추기 움직임 속 상한가 기록. 15% 이상 상승 및 연상 기대감 형성.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['임상', '기술 이전', 'FDA']</t>
+          <t>['흥구석유', '키맞추기', '연상']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>004090</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>한국석유</t>
+          <t>카프로</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12920</v>
+        <v>164</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+11.86%</t>
+          <t>+11.56%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.26</v>
+        <v>-0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="F8" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G8" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="H8" t="n">
-        <v>4.37</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>11550</v>
+        <v>147</v>
       </c>
       <c r="K8" t="n">
-        <v>11780</v>
+        <v>181</v>
       </c>
       <c r="L8" t="n">
-        <v>14880</v>
+        <v>260</v>
       </c>
       <c r="M8" t="n">
-        <v>11700</v>
+        <v>164</v>
       </c>
       <c r="N8" t="n">
-        <v>4.63</v>
+        <v>0.08</v>
       </c>
       <c r="O8" t="n">
-        <v>93101656125</v>
+        <v>632864490</v>
       </c>
       <c r="P8" t="n">
-        <v>33575</v>
+        <v>3660</v>
       </c>
       <c r="Q8" t="n">
-        <v>9690</v>
+        <v>133</v>
       </c>
       <c r="R8" t="n">
-        <v>-78000</v>
+        <v>-18000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>흥구석유와 키 맞추기 움직임 속 상한가 기록. 15% 이상 상승 및 연상 기대감 형성.</t>
+          <t>거래량 급증하며 60% 이상 급등. 회생 및 상장 기대감 속 추격매수 의견.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['흥구석유', '키맞추기', '연상']</t>
+          <t>['급등', '거래량', '회생']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>004090</t>
+          <t>006380</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1942</v>
+        <v>1931</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+10.34%</t>
+          <t>+9.72%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F9" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G9" t="n">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="H9" t="n">
         <v>2.12</v>
@@ -1254,7 +1254,7 @@
         <v>2.07</v>
       </c>
       <c r="O9" t="n">
-        <v>182889478885</v>
+        <v>183468755909</v>
       </c>
       <c r="P9" t="n">
         <v>4795</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>외인 매수세 유입에도 불구하고 잦은 등락과 급락 반복, 주가 부양 의지에 대한 의문 제기. 120일선 돌파 기대와 함께 향후 추세에 대한 불확실성 상존.</t>
+          <t>주가 하락세 속 외인 매수세 유입, 단기 반등 기대감 존재하나 불확실.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['외인', '120일선', '주포']</t>
+          <t>['외인매수', '주가흐름', '단기반등']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>좋은사람들</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2125</v>
+        <v>516</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+1.92%</t>
+          <t>+1.57%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="E10" t="n">
-        <v>119</v>
+        <v>61</v>
       </c>
       <c r="F10" t="n">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="G10" t="n">
-        <v>207</v>
+        <v>65</v>
       </c>
       <c r="H10" t="n">
-        <v>0.85</v>
+        <v>2.8</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,91 +1331,91 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>2085</v>
+        <v>508</v>
       </c>
       <c r="K10" t="n">
-        <v>2255</v>
+        <v>510</v>
       </c>
       <c r="L10" t="n">
-        <v>2395</v>
+        <v>585</v>
       </c>
       <c r="M10" t="n">
-        <v>2040</v>
+        <v>504</v>
       </c>
       <c r="N10" t="n">
-        <v>0.51</v>
+        <v>2.42</v>
       </c>
       <c r="O10" t="n">
-        <v>18866124773</v>
+        <v>8051896154</v>
       </c>
       <c r="P10" t="n">
-        <v>2930</v>
+        <v>2610</v>
       </c>
       <c r="Q10" t="n">
-        <v>910</v>
+        <v>255</v>
       </c>
       <c r="R10" t="n">
-        <v>-175000</v>
+        <v>-263000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>새만금 개발 및 LH 관련 호재 속 기관 및 기타 법인 매수세 유입.</t>
+          <t>액면병합 후 상승 기대와 상폐 경고가 혼재. 사실 여부 불분명한 정보 속 투자자 혼란.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['새만금', 'LH']</t>
+          <t>['상폐', '병합', '감자']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>033340</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>좋은사람들</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>516</v>
+        <v>2110</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>+1.20%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.38</v>
+        <v>0.34</v>
       </c>
       <c r="E11" t="n">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="F11" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="G11" t="n">
-        <v>61</v>
+        <v>210</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8</v>
+        <v>0.85</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,60 +1423,60 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>508</v>
+        <v>2085</v>
       </c>
       <c r="K11" t="n">
-        <v>510</v>
+        <v>2255</v>
       </c>
       <c r="L11" t="n">
-        <v>585</v>
+        <v>2395</v>
       </c>
       <c r="M11" t="n">
-        <v>504</v>
+        <v>2040</v>
       </c>
       <c r="N11" t="n">
-        <v>2.42</v>
+        <v>0.51</v>
       </c>
       <c r="O11" t="n">
-        <v>8018423998</v>
+        <v>19066369538</v>
       </c>
       <c r="P11" t="n">
-        <v>2610</v>
+        <v>2930</v>
       </c>
       <c r="Q11" t="n">
-        <v>255</v>
+        <v>910</v>
       </c>
       <c r="R11" t="n">
-        <v>-263000</v>
+        <v>-175000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>액면병합 후 상승 기대와 상폐 경고가 혼재. 사실 여부 불분명한 정보 속 투자자 혼란.</t>
+          <t>새만금 및 LH 관련 사업 기대감 속에서 매집 움직임 포착, 주가 상승 가능성.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['상폐', '병합', '감자']</t>
+          <t>['새만금', 'LH', '매집']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>033340</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3860</v>
+        <v>3850</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+1.31%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-1.62</v>
       </c>
       <c r="E12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G12" t="n">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="H12" t="n">
         <v>1.57</v>
@@ -1530,7 +1530,7 @@
         <v>3.19</v>
       </c>
       <c r="O12" t="n">
-        <v>131505871944</v>
+        <v>132115238180</v>
       </c>
       <c r="P12" t="n">
         <v>8100</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>투기과열종목 지정 회피 및 5G/6G 관련 신규 수주 기대감. 주포의 흔들기에 따른 단기 변동성 전망.</t>
+          <t>투기과열종목 지정 회피, 5G/6G 관련 사업 기대감으로 인한 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['투경', '신규 수주', '5G']</t>
+          <t>['투기과열', '5G', '6G']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1848000</v>
+        <v>153100</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.01</v>
+        <v>0.4</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>371</v>
       </c>
       <c r="F13" t="n">
-        <v>468</v>
+        <v>173</v>
       </c>
       <c r="G13" t="n">
-        <v>1870</v>
+        <v>930</v>
       </c>
       <c r="H13" t="n">
-        <v>50.67</v>
+        <v>15.65</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1856000</v>
+        <v>153500</v>
       </c>
       <c r="K13" t="n">
-        <v>1879000</v>
+        <v>155500</v>
       </c>
       <c r="L13" t="n">
-        <v>1890000</v>
+        <v>164700</v>
       </c>
       <c r="M13" t="n">
-        <v>1811000</v>
+        <v>150200</v>
       </c>
       <c r="N13" t="n">
-        <v>50.66</v>
+        <v>15.25</v>
       </c>
       <c r="O13" t="n">
-        <v>3484080667000</v>
+        <v>332062893700</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>164700</v>
       </c>
       <c r="Q13" t="n">
-        <v>293000</v>
+        <v>87700</v>
       </c>
       <c r="R13" t="n">
-        <v>-110000</v>
+        <v>104000</v>
       </c>
       <c r="S13" t="n">
-        <v>-78000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>30만원 재돌파 기대감 및 연기금 리밸런싱 흐름 분석. 외국인 매도세 관찰.</t>
+          <t>유가 상승으로 인한 SK이노베이션 주가 상승 기대감, 투자 심리 긍정적.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['반도체', '외국인']</t>
+          <t>['유가상승', '주가상승', '투자심리']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>152100</v>
+        <v>1849000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.91%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.4</v>
+        <v>0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>366</v>
+        <v>799</v>
       </c>
       <c r="F14" t="n">
-        <v>171</v>
+        <v>471</v>
       </c>
       <c r="G14" t="n">
-        <v>916</v>
+        <v>1923</v>
       </c>
       <c r="H14" t="n">
-        <v>15.65</v>
+        <v>50.67</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>153500</v>
+        <v>1856000</v>
       </c>
       <c r="K14" t="n">
-        <v>155500</v>
+        <v>1879000</v>
       </c>
       <c r="L14" t="n">
-        <v>164700</v>
+        <v>1890000</v>
       </c>
       <c r="M14" t="n">
-        <v>150200</v>
+        <v>1811000</v>
       </c>
       <c r="N14" t="n">
-        <v>15.25</v>
+        <v>50.66</v>
       </c>
       <c r="O14" t="n">
-        <v>329206458650</v>
+        <v>3534834099000</v>
       </c>
       <c r="P14" t="n">
-        <v>164700</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>87700</v>
+        <v>293000</v>
       </c>
       <c r="R14" t="n">
-        <v>104000</v>
+        <v>-110000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-78000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>유가 급등에 따른 기대감 속 일부 투자자들의 이익 실현 및 관망세. 외국인 대량 매집 패턴 분석.</t>
+          <t>SK하이닉스 주가 상승 추세, 대규모 자사주 매입 및 리밸런싱 효과 기대.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['유가', '외국인']</t>
+          <t>['주가상승', '자사주매입', '리밸런싱']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1774,13 +1774,13 @@
         <v>-0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="F15" t="n">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G15" t="n">
-        <v>1289</v>
+        <v>1265</v>
       </c>
       <c r="H15" t="n">
         <v>46.81</v>
@@ -1806,7 +1806,7 @@
         <v>46.85</v>
       </c>
       <c r="O15" t="n">
-        <v>2033732782250</v>
+        <v>2052664549250</v>
       </c>
       <c r="P15" t="n">
         <v>374500</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>자사주 매입 호재에도 불구하고 부정적인 전망과 매도 의견이 우세.</t>
+          <t>삼성전자 주가 하락 및 실적 부진 전망, 매도 의견 다수.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['자사주 매입']</t>
+          <t>['주가하락', '실적부진', '매도의견']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14030</v>
+        <v>14080</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.03%</t>
+          <t>-1.68%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0.45</v>
       </c>
       <c r="E16" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G16" t="n">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="H16" t="n">
         <v>6.09</v>
@@ -1898,7 +1898,7 @@
         <v>5.64</v>
       </c>
       <c r="O16" t="n">
-        <v>122739266155</v>
+        <v>125224573565</v>
       </c>
       <c r="P16" t="n">
         <v>30200</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>원전주로서 미국 신규 원전 건설 이슈와 연계된 상승 기대감. 공매도 금지 및 세력 개입 가능성 언급. 단기 급등 후 조정 및 관망세 혼재.</t>
+          <t>미국 신규 원전 건설 및 공매도 금지 이슈로 우리기술 주가 상승 기대감.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['원전', '공매도', '세력']</t>
+          <t>['원전주', '공매도금지', '주가상승']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19000</v>
+        <v>19030</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.31%</t>
+          <t>-2.16%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.21</v>
       </c>
       <c r="E17" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F17" t="n">
         <v>62</v>
       </c>
       <c r="G17" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="H17" t="n">
         <v>10.64</v>
@@ -1990,7 +1990,7 @@
         <v>10.85</v>
       </c>
       <c r="O17" t="n">
-        <v>73794863120</v>
+        <v>74627221805</v>
       </c>
       <c r="P17" t="n">
         <v>40350</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6690</v>
+        <v>6700</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.48%</t>
+          <t>-2.33%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-1.03</v>
       </c>
       <c r="E18" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F18" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G18" t="n">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="H18" t="n">
         <v>15.68</v>
@@ -2082,7 +2082,7 @@
         <v>16.71</v>
       </c>
       <c r="O18" t="n">
-        <v>11095964050</v>
+        <v>11373008115</v>
       </c>
       <c r="P18" t="n">
         <v>13000</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>89000</v>
+        <v>89100</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.94%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>0.04</v>
       </c>
       <c r="E19" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F19" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G19" t="n">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="H19" t="n">
         <v>23.65</v>
@@ -2174,7 +2174,7 @@
         <v>23.61</v>
       </c>
       <c r="O19" t="n">
-        <v>135483280550</v>
+        <v>136874174500</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2234,13 +2234,13 @@
         <v>1.34</v>
       </c>
       <c r="E20" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F20" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G20" t="n">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="H20" t="n">
         <v>2.89</v>
@@ -2266,7 +2266,7 @@
         <v>1.55</v>
       </c>
       <c r="O20" t="n">
-        <v>78532828960</v>
+        <v>79334497050</v>
       </c>
       <c r="P20" t="n">
         <v>31500</v>
@@ -2282,12 +2282,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 광통신 및 AI 관련주 동반 강세에 따른 상승 추세 전망. 외인 매수세 유입 및 120일선 돌파 시도. 16000원 돌파 및 5만원까지 목표가 제시.</t>
+          <t>미국 광통신 관련주로 분류되며, 외인 매수세 유입 및 AI 관련주로서의 기대감이 형성되고 있음. 다만, 주가 변동성이 관찰됨.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14930</v>
+        <v>14960</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-4.54%</t>
+          <t>-4.35%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F21" t="n">
         <v>65</v>
       </c>
       <c r="G21" t="n">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2358,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>22357846760</v>
+        <v>22550178915</v>
       </c>
       <c r="P21" t="n">
         <v>19380</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>킨텍스 공시 수주 및 호남 반도체 설계 용역 발주 관련 긍정적 뉴스 기반 상승 기대. 수주 잔고 증가 및 흑자 전환 전망. 14000원대 지지선 및 분할 매수 기회 제시.</t>
+          <t>LH 발주 반도체 설계 용역 수주 및 킨텍스 공시 등 실질적인 수주 내용이 언급되며, 긍정적인 전망이 나오고 있음. 수주잔고 및 흑자 전환 가능성에 대한 기대가 존재함.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['수주', '공시', '반도체']</t>
+          <t>['수주', '공시', '건설']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29450</v>
+        <v>29550</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-5.31%</t>
+          <t>-4.98%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2450,7 +2450,7 @@
         <v>12.14</v>
       </c>
       <c r="O22" t="n">
-        <v>52212910675</v>
+        <v>52863268750</v>
       </c>
       <c r="P22" t="n">
         <v>75900</v>
@@ -2499,21 +2499,21 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3645</v>
+        <v>3650</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-5.69%</t>
+          <t>-5.56%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-0.54</v>
       </c>
       <c r="E23" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F23" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G23" t="n">
         <v>133</v>
@@ -2542,7 +2542,7 @@
         <v>2.08</v>
       </c>
       <c r="O23" t="n">
-        <v>46825212398</v>
+        <v>47443026018</v>
       </c>
       <c r="P23" t="n">
         <v>4335</v>
@@ -2591,11 +2591,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2125</v>
+        <v>2115</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-5.97%</t>
+          <t>-6.42%</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -2608,7 +2608,7 @@
         <v>43</v>
       </c>
       <c r="G24" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H24" t="n">
         <v>4.91</v>
@@ -2634,7 +2634,7 @@
         <v>5.26</v>
       </c>
       <c r="O24" t="n">
-        <v>5957115842</v>
+        <v>6024412892</v>
       </c>
       <c r="P24" t="n">
         <v>2705</v>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>M&amp;A 관련 이슈와 신규 최대주주 등장 가능성 속에서 주가 변동성 확대. 1만원 돌파 기대감과 동시에 하한가 예상 등 상반된 전망 혼재. 유증 및 적대적 M&amp;A 관련 논쟁 지속.</t>
+          <t>M&amp;A 관련 이슈로 인한 변동성 확대, 적대적 M&amp;A 가능성 및 신주인수 영향.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['M&amp;A', '최대주주', '유증']</t>
+          <t>['M&amp;A', '신주인수', '변동성']</t>
         </is>
       </c>
       <c r="X24" t="n">
@@ -2694,13 +2694,13 @@
         <v>-0.22</v>
       </c>
       <c r="E25" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F25" t="n">
         <v>59</v>
       </c>
       <c r="G25" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="H25" t="n">
         <v>0.14</v>
@@ -2726,7 +2726,7 @@
         <v>0.36</v>
       </c>
       <c r="O25" t="n">
-        <v>62202957350</v>
+        <v>62682643290</v>
       </c>
       <c r="P25" t="n">
         <v>20850</v>
@@ -2742,16 +2742,16 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>그래핀 관련 대규모 계약 기대감 속 일부 투자자들의 이익 실현. 프로그램 매수세 관찰 및 추가 매수 대기.</t>
+          <t>그래핀 신소재 관련 언급과 함께 최대 호재 가능성이 제기되나, 구체적인 공시나 뉴스가 부족하여 기대감 위주의 논의가 진행됨.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['그래핀', '대규모 계약', '프로그램 매수']</t>
+          <t>['그래핀', '신소재', '호재']</t>
         </is>
       </c>
       <c r="X25" t="n">
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>27850</v>
+        <v>27950</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-8.09%</t>
+          <t>-7.76%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.02</v>
       </c>
       <c r="E26" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F26" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G26" t="n">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="H26" t="n">
         <v>0.33</v>
@@ -2818,7 +2818,7 @@
         <v>0.31</v>
       </c>
       <c r="O26" t="n">
-        <v>117411839375</v>
+        <v>117889605300</v>
       </c>
       <c r="P26" t="n">
         <v>39350</v>
@@ -2867,11 +2867,11 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-43.95%</t>
+          <t>-44.76%</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -2884,7 +2884,7 @@
         <v>41</v>
       </c>
       <c r="G27" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H27" t="n">
         <v>5.86</v>
@@ -2910,7 +2910,7 @@
         <v>6.18</v>
       </c>
       <c r="O27" t="n">
-        <v>800179694</v>
+        <v>837239701</v>
       </c>
       <c r="P27" t="n">
         <v>901</v>

--- a/data/trending_integrated_20260910_12.xlsx
+++ b/data/trending_integrated_20260910_12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z27"/>
+  <dimension ref="A1:Z28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4450</v>
+        <v>4185</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+122.50%</t>
+          <t>+109.25%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="F2" t="n">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="G2" t="n">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="H2" t="n">
         <v>3.2</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>639673444784</v>
+        <v>652408874139</v>
       </c>
       <c r="P2" t="n">
         <v>5700</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>스팩주 합병 관련 불확실성 속에서 단기 급등 가능성 언급, 투자 주의 필요.</t>
+          <t>신재생에너지 합병 대상 스팩주. 6천원~2천원대 예측 및 300% 상승 기대감 공존.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스팩주', '합병', '단기급등']</t>
+          <t>['스팩주', '신재생에너지', '합병']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29150</v>
+        <v>29275</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+25.65%</t>
+          <t>+26.19%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F3" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H3" t="n">
         <v>7.54</v>
@@ -702,7 +702,7 @@
         <v>7.58</v>
       </c>
       <c r="O3" t="n">
-        <v>43468863975</v>
+        <v>43796798325</v>
       </c>
       <c r="P3" t="n">
         <v>34750</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14690</v>
+        <v>14740</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+21.51%</t>
+          <t>+21.92%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.03</v>
       </c>
       <c r="E4" t="n">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="F4" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G4" t="n">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H4" t="n">
         <v>0.03</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>274433757925</v>
+        <v>276846328175</v>
       </c>
       <c r="P4" t="n">
         <v>36200</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>국제 유가 급등 및 지정학적 리스크 고조로 흥구석유 주가 급등, 추가 상승 기대.</t>
+          <t>이란발 지정학적 리스크 및 유가 급등 전망. WTI 110달러 돌파 및 급등 예상.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['국제유가', '지정학적리스크', '주가급등']</t>
+          <t>['유가', '이란', '호르무즈']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,18 +843,18 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3565</v>
+        <v>3645</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+14.81%</t>
+          <t>+17.39%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F5" t="n">
         <v>40</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>23411570765</v>
+        <v>23755545846</v>
       </c>
       <c r="P5" t="n">
         <v>20800</v>
@@ -931,184 +931,184 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>한국석유</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8340</v>
+        <v>13100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+12.40%</t>
+          <t>+13.42%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.4</v>
+        <v>-0.26</v>
       </c>
       <c r="E6" t="n">
-        <v>244</v>
+        <v>69</v>
       </c>
       <c r="F6" t="n">
-        <v>110</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>1283</v>
+        <v>42</v>
       </c>
       <c r="H6" t="n">
-        <v>1.17</v>
+        <v>4.37</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>7420</v>
+        <v>11550</v>
       </c>
       <c r="K6" t="n">
-        <v>8000</v>
+        <v>11780</v>
       </c>
       <c r="L6" t="n">
-        <v>9100</v>
+        <v>14880</v>
       </c>
       <c r="M6" t="n">
-        <v>7930</v>
+        <v>11700</v>
       </c>
       <c r="N6" t="n">
-        <v>0.77</v>
+        <v>4.63</v>
       </c>
       <c r="O6" t="n">
-        <v>64102836990</v>
+        <v>94251190435</v>
       </c>
       <c r="P6" t="n">
-        <v>21500</v>
+        <v>33575</v>
       </c>
       <c r="Q6" t="n">
-        <v>2300</v>
+        <v>9690</v>
       </c>
       <c r="R6" t="n">
-        <v>117000</v>
+        <v>-78000</v>
       </c>
       <c r="S6" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>글로벌 제약사와의 임상 참여 및 기술 이전 기대감으로 인한 급등 전망.</t>
+          <t>흥구석유와 키 맞추기 움직임 속 상한가 기록. 15% 이상 상승 및 연상 기대감 형성.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['임상', '기술 이전', 'FDA']</t>
+          <t>['흥구석유', '키맞추기', '연상']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>004090</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>한국석유</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12920</v>
+        <v>8340</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+11.86%</t>
+          <t>+12.40%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.26</v>
+        <v>0.4</v>
       </c>
       <c r="E7" t="n">
-        <v>68</v>
+        <v>249</v>
       </c>
       <c r="F7" t="n">
-        <v>41</v>
+        <v>111</v>
       </c>
       <c r="G7" t="n">
-        <v>40</v>
+        <v>1297</v>
       </c>
       <c r="H7" t="n">
-        <v>4.37</v>
+        <v>1.17</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>11550</v>
+        <v>7420</v>
       </c>
       <c r="K7" t="n">
-        <v>11780</v>
+        <v>8000</v>
       </c>
       <c r="L7" t="n">
-        <v>14880</v>
+        <v>9100</v>
       </c>
       <c r="M7" t="n">
-        <v>11700</v>
+        <v>7930</v>
       </c>
       <c r="N7" t="n">
-        <v>4.63</v>
+        <v>0.77</v>
       </c>
       <c r="O7" t="n">
-        <v>93430897455</v>
+        <v>64611309745</v>
       </c>
       <c r="P7" t="n">
-        <v>33575</v>
+        <v>21500</v>
       </c>
       <c r="Q7" t="n">
-        <v>9690</v>
+        <v>2300</v>
       </c>
       <c r="R7" t="n">
-        <v>-78000</v>
+        <v>117000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>흥구석유와 키 맞추기 움직임 속 상한가 기록. 15% 이상 상승 및 연상 기대감 형성.</t>
+          <t>글로벌 제약사와의 임상 참여 및 기술 이전 기대감으로 인한 급등 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['흥구석유', '키맞추기', '연상']</t>
+          <t>['임상', '기술 이전', 'FDA']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>004090</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
         <v>-0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F8" t="n">
         <v>36</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1931</v>
+        <v>1934</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+9.72%</t>
+          <t>+9.89%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F9" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G9" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H9" t="n">
         <v>2.12</v>
@@ -1254,7 +1254,7 @@
         <v>2.07</v>
       </c>
       <c r="O9" t="n">
-        <v>183468755909</v>
+        <v>184843220372</v>
       </c>
       <c r="P9" t="n">
         <v>4795</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>주가 하락세 속 외인 매수세 유입, 단기 반등 기대감 존재하나 불확실.</t>
+          <t>외인 매수세 유입 속 주가 급등락 반복. 120일선 돌파 기대감과 급락 우려 상존.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['외인매수', '주가흐름', '단기반등']</t>
+          <t>['외인', '급등락', '120일선']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,79 +1299,79 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>좋은사람들</t>
+          <t>넥스틸</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>516</v>
+        <v>14430</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>+8.41%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.38</v>
+        <v>-0.53</v>
       </c>
       <c r="E10" t="n">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="F10" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="G10" t="n">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8</v>
+        <v>0.57</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>508</v>
+        <v>13310</v>
       </c>
       <c r="K10" t="n">
-        <v>510</v>
+        <v>13540</v>
       </c>
       <c r="L10" t="n">
-        <v>585</v>
+        <v>16100</v>
       </c>
       <c r="M10" t="n">
-        <v>504</v>
+        <v>13460</v>
       </c>
       <c r="N10" t="n">
-        <v>2.42</v>
+        <v>1.1</v>
       </c>
       <c r="O10" t="n">
-        <v>8051896154</v>
+        <v>112564301955</v>
       </c>
       <c r="P10" t="n">
-        <v>2610</v>
+        <v>23000</v>
       </c>
       <c r="Q10" t="n">
-        <v>255</v>
+        <v>9030</v>
       </c>
       <c r="R10" t="n">
-        <v>-263000</v>
+        <v>33000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>액면병합 후 상승 기대와 상폐 경고가 혼재. 사실 여부 불분명한 정보 속 투자자 혼란.</t>
+          <t>중동 강관 수출 기대감 속 주가 상승. 재무제표 기반 3만원 이상 목표치 제시.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['상폐', '병합', '감자']</t>
+          <t>['중동', '강관', '재무제표']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1379,43 +1379,43 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>033340</t>
+          <t>092790</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>좋은사람들</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2110</v>
+        <v>518</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+1.20%</t>
+          <t>+1.97%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="E11" t="n">
-        <v>122</v>
+        <v>60</v>
       </c>
       <c r="F11" t="n">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="G11" t="n">
-        <v>210</v>
+        <v>60</v>
       </c>
       <c r="H11" t="n">
-        <v>0.85</v>
+        <v>2.8</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,60 +1423,60 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>2085</v>
+        <v>508</v>
       </c>
       <c r="K11" t="n">
-        <v>2255</v>
+        <v>510</v>
       </c>
       <c r="L11" t="n">
-        <v>2395</v>
+        <v>585</v>
       </c>
       <c r="M11" t="n">
-        <v>2040</v>
+        <v>504</v>
       </c>
       <c r="N11" t="n">
-        <v>0.51</v>
+        <v>2.42</v>
       </c>
       <c r="O11" t="n">
-        <v>19066369538</v>
+        <v>8102885494</v>
       </c>
       <c r="P11" t="n">
-        <v>2930</v>
+        <v>2610</v>
       </c>
       <c r="Q11" t="n">
-        <v>910</v>
+        <v>255</v>
       </c>
       <c r="R11" t="n">
-        <v>-175000</v>
+        <v>-263000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>새만금 및 LH 관련 사업 기대감 속에서 매집 움직임 포착, 주가 상승 가능성.</t>
+          <t>액면병합 후 상승 기대와 상폐 경고가 혼재. 사실 여부 불분명한 정보 속 투자자 혼란.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['새만금', 'LH', '매집']</t>
+          <t>['상폐', '병합', '감자']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>033340</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3850</v>
+        <v>3885</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+1.05%</t>
+          <t>+1.97%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-1.62</v>
       </c>
       <c r="E12" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F12" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G12" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H12" t="n">
         <v>1.57</v>
@@ -1530,7 +1530,7 @@
         <v>3.19</v>
       </c>
       <c r="O12" t="n">
-        <v>132115238180</v>
+        <v>133785053743</v>
       </c>
       <c r="P12" t="n">
         <v>8100</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>투기과열종목 지정 회피, 5G/6G 관련 사업 기대감으로 인한 주가 상승 전망.</t>
+          <t>투기과열종목 지정 회피 및 6G 통신 테마 기대감. 15% 상승 전망 및 10버거 목표 제시.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['투기과열', '5G', '6G']</t>
+          <t>['투기과열', '6G', '통신']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,83 +1575,83 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>153100</v>
+        <v>2105</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="E13" t="n">
-        <v>371</v>
+        <v>122</v>
       </c>
       <c r="F13" t="n">
-        <v>173</v>
+        <v>54</v>
       </c>
       <c r="G13" t="n">
-        <v>930</v>
+        <v>212</v>
       </c>
       <c r="H13" t="n">
-        <v>15.65</v>
+        <v>0.85</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>153500</v>
+        <v>2085</v>
       </c>
       <c r="K13" t="n">
-        <v>155500</v>
+        <v>2255</v>
       </c>
       <c r="L13" t="n">
-        <v>164700</v>
+        <v>2395</v>
       </c>
       <c r="M13" t="n">
-        <v>150200</v>
+        <v>2040</v>
       </c>
       <c r="N13" t="n">
-        <v>15.25</v>
+        <v>0.51</v>
       </c>
       <c r="O13" t="n">
-        <v>332062893700</v>
+        <v>19163103298</v>
       </c>
       <c r="P13" t="n">
-        <v>164700</v>
+        <v>2930</v>
       </c>
       <c r="Q13" t="n">
-        <v>87700</v>
+        <v>910</v>
       </c>
       <c r="R13" t="n">
-        <v>104000</v>
+        <v>-175000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>유가 상승으로 인한 SK이노베이션 주가 상승 기대감, 투자 심리 긍정적.</t>
+          <t>새만금 및 LH 관련 사업 기대감 속에서 매집 움직임 포착, 주가 상승 가능성.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['유가상승', '주가상승', '투자심리']</t>
+          <t>['새만금', 'LH', '매집']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1849000</v>
+        <v>154300</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.01</v>
+        <v>0.4</v>
       </c>
       <c r="E14" t="n">
-        <v>799</v>
+        <v>377</v>
       </c>
       <c r="F14" t="n">
-        <v>471</v>
+        <v>176</v>
       </c>
       <c r="G14" t="n">
-        <v>1923</v>
+        <v>951</v>
       </c>
       <c r="H14" t="n">
-        <v>50.67</v>
+        <v>15.65</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1856000</v>
+        <v>153500</v>
       </c>
       <c r="K14" t="n">
-        <v>1879000</v>
+        <v>155500</v>
       </c>
       <c r="L14" t="n">
-        <v>1890000</v>
+        <v>164700</v>
       </c>
       <c r="M14" t="n">
-        <v>1811000</v>
+        <v>150200</v>
       </c>
       <c r="N14" t="n">
-        <v>50.66</v>
+        <v>15.25</v>
       </c>
       <c r="O14" t="n">
-        <v>3534834099000</v>
+        <v>342328455550</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>164700</v>
       </c>
       <c r="Q14" t="n">
-        <v>293000</v>
+        <v>87700</v>
       </c>
       <c r="R14" t="n">
-        <v>-110000</v>
+        <v>104000</v>
       </c>
       <c r="S14" t="n">
-        <v>-78000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>SK하이닉스 주가 상승 추세, 대규모 자사주 매입 및 리밸런싱 효과 기대.</t>
+          <t>유가 상승으로 인한 SK이노베이션 주가 상승 기대감, 투자 심리 긍정적.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주가상승', '자사주매입', '리밸런싱']</t>
+          <t>['유가상승', '주가상승', '투자심리']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>267000</v>
+        <v>1844000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>-0.65%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>793</v>
+        <v>799</v>
       </c>
       <c r="F15" t="n">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="G15" t="n">
-        <v>1265</v>
+        <v>1938</v>
       </c>
       <c r="H15" t="n">
-        <v>46.81</v>
+        <v>50.67</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>269500</v>
+        <v>1856000</v>
       </c>
       <c r="K15" t="n">
-        <v>269000</v>
+        <v>1879000</v>
       </c>
       <c r="L15" t="n">
-        <v>270500</v>
+        <v>1890000</v>
       </c>
       <c r="M15" t="n">
-        <v>263500</v>
+        <v>1811000</v>
       </c>
       <c r="N15" t="n">
-        <v>46.85</v>
+        <v>50.66</v>
       </c>
       <c r="O15" t="n">
-        <v>2052664549250</v>
+        <v>3616217989500</v>
       </c>
       <c r="P15" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q15" t="n">
-        <v>71600</v>
+        <v>293000</v>
       </c>
       <c r="R15" t="n">
-        <v>376000</v>
+        <v>-110000</v>
       </c>
       <c r="S15" t="n">
-        <v>-400000</v>
+        <v>-78000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>삼성전자 주가 하락 및 실적 부진 전망, 매도 의견 다수.</t>
+          <t>SK하이닉스 주가 상승 추세, 대규모 자사주 매입 및 리밸런싱 효과 기대.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가하락', '실적부진', '매도의견']</t>
+          <t>['주가상승', '자사주매입', '리밸런싱']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>103</v>
+        <v>68</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14080</v>
+        <v>267250</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.68%</t>
+          <t>-0.83%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.45</v>
+        <v>-0.04</v>
       </c>
       <c r="E16" t="n">
-        <v>103</v>
+        <v>793</v>
       </c>
       <c r="F16" t="n">
-        <v>64</v>
+        <v>471</v>
       </c>
       <c r="G16" t="n">
-        <v>582</v>
+        <v>1272</v>
       </c>
       <c r="H16" t="n">
-        <v>6.09</v>
+        <v>46.81</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>14320</v>
+        <v>269500</v>
       </c>
       <c r="K16" t="n">
-        <v>13800</v>
+        <v>269000</v>
       </c>
       <c r="L16" t="n">
-        <v>14400</v>
+        <v>270500</v>
       </c>
       <c r="M16" t="n">
-        <v>13260</v>
+        <v>263500</v>
       </c>
       <c r="N16" t="n">
-        <v>5.64</v>
+        <v>46.85</v>
       </c>
       <c r="O16" t="n">
-        <v>125224573565</v>
+        <v>2121469276000</v>
       </c>
       <c r="P16" t="n">
-        <v>30200</v>
+        <v>374500</v>
       </c>
       <c r="Q16" t="n">
-        <v>3540</v>
+        <v>71600</v>
       </c>
       <c r="R16" t="n">
-        <v>-132000</v>
+        <v>376000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-400000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 신규 원전 건설 및 공매도 금지 이슈로 우리기술 주가 상승 기대감.</t>
+          <t>하이닉스 대비 상승세 미미. 악재 누적 및 매도 의견 우세 속 주가 하락 전망.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['원전주', '공매도금지', '주가상승']</t>
+          <t>['하이닉스', '매도', '악재']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,90 +1936,90 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19030</v>
+        <v>14100</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.16%</t>
+          <t>-1.54%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.21</v>
+        <v>0.45</v>
       </c>
       <c r="E17" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F17" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G17" t="n">
-        <v>347</v>
+        <v>590</v>
       </c>
       <c r="H17" t="n">
-        <v>10.64</v>
+        <v>6.09</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>19450</v>
+        <v>14320</v>
       </c>
       <c r="K17" t="n">
-        <v>18900</v>
+        <v>13800</v>
       </c>
       <c r="L17" t="n">
-        <v>19220</v>
+        <v>14400</v>
       </c>
       <c r="M17" t="n">
-        <v>18670</v>
+        <v>13260</v>
       </c>
       <c r="N17" t="n">
-        <v>10.85</v>
+        <v>5.64</v>
       </c>
       <c r="O17" t="n">
-        <v>74627221805</v>
+        <v>126346035695</v>
       </c>
       <c r="P17" t="n">
-        <v>40350</v>
+        <v>30200</v>
       </c>
       <c r="Q17" t="n">
-        <v>3320</v>
+        <v>3540</v>
       </c>
       <c r="R17" t="n">
-        <v>-67000</v>
+        <v>-132000</v>
       </c>
       <c r="S17" t="n">
-        <v>-52000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 투자 관련 기대감 속에서 주가 상승 전망 제시. 다만, 주주들의 대차해지 동참 요구가 반복되며 주가 부양을 위한 주주 행동 촉구. 실제 팩트 기반 분석은 부족.</t>
+          <t>미국 신규 원전 건설 및 공매도 금지 이슈로 우리기술 주가 상승 기대감.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['미국 투자', '대차해지', '원전']</t>
+          <t>['원전주', '공매도금지', '주가상승']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>6700</v>
+        <v>19010</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.33%</t>
+          <t>-2.26%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-1.03</v>
+        <v>-0.21</v>
       </c>
       <c r="E18" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F18" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G18" t="n">
-        <v>295</v>
+        <v>359</v>
       </c>
       <c r="H18" t="n">
-        <v>15.68</v>
+        <v>10.64</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,51 +2067,51 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>6860</v>
+        <v>19450</v>
       </c>
       <c r="K18" t="n">
-        <v>6800</v>
+        <v>18900</v>
       </c>
       <c r="L18" t="n">
-        <v>6820</v>
+        <v>19220</v>
       </c>
       <c r="M18" t="n">
-        <v>6400</v>
+        <v>18670</v>
       </c>
       <c r="N18" t="n">
-        <v>16.71</v>
+        <v>10.85</v>
       </c>
       <c r="O18" t="n">
-        <v>11373008115</v>
+        <v>76155136965</v>
       </c>
       <c r="P18" t="n">
-        <v>13000</v>
+        <v>40350</v>
       </c>
       <c r="Q18" t="n">
-        <v>6030</v>
+        <v>3320</v>
       </c>
       <c r="R18" t="n">
-        <v>-273000</v>
+        <v>-67000</v>
       </c>
       <c r="S18" t="n">
-        <v>-10000</v>
+        <v>-52000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>외국인 매도세 및 분사 관련 불확실성 속 기관의 관망세. 주가 조작 및 패턴 반복에 대한 불만 제기.</t>
+          <t>미국 투자 기대감과 대차해지 운동 동참 호소. 주주들의 적극적인 참여 독려.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['외국인', '기관', '분사']</t>
+          <t>['미국 투자', '대차해지', '주주']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>89100</v>
+        <v>6670</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.84%</t>
+          <t>-2.77%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.04</v>
+        <v>-1.03</v>
       </c>
       <c r="E19" t="n">
-        <v>222</v>
+        <v>108</v>
       </c>
       <c r="F19" t="n">
-        <v>144</v>
+        <v>60</v>
       </c>
       <c r="G19" t="n">
-        <v>769</v>
+        <v>304</v>
       </c>
       <c r="H19" t="n">
-        <v>23.65</v>
+        <v>15.68</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,51 +2159,51 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>91700</v>
+        <v>6860</v>
       </c>
       <c r="K19" t="n">
-        <v>90000</v>
+        <v>6800</v>
       </c>
       <c r="L19" t="n">
-        <v>90700</v>
+        <v>6820</v>
       </c>
       <c r="M19" t="n">
-        <v>87800</v>
+        <v>6400</v>
       </c>
       <c r="N19" t="n">
-        <v>23.61</v>
+        <v>16.71</v>
       </c>
       <c r="O19" t="n">
-        <v>136874174500</v>
+        <v>11641052955</v>
       </c>
       <c r="P19" t="n">
-        <v>139200</v>
+        <v>13000</v>
       </c>
       <c r="Q19" t="n">
-        <v>57000</v>
+        <v>6030</v>
       </c>
       <c r="R19" t="n">
         <v>-273000</v>
       </c>
       <c r="S19" t="n">
-        <v>31000</v>
+        <v>-10000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 원전 건설 '팀코리아' 및 웨스턴하우스 지분 인수 가능성, 역사적 호재 언급.</t>
+          <t>외국인 매도세 및 분사 관련 불확실성 속 기관의 관망세. 주가 조작 및 패턴 반복에 대한 불만 제기.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['원전', '웨스턴하우스', '호재']</t>
+          <t>['외국인', '기관', '분사']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,86 +2212,86 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14380</v>
+        <v>88800</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.88%</t>
+          <t>-3.16%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.34</v>
+        <v>0.04</v>
       </c>
       <c r="E20" t="n">
-        <v>132</v>
+        <v>224</v>
       </c>
       <c r="F20" t="n">
-        <v>70</v>
+        <v>145</v>
       </c>
       <c r="G20" t="n">
-        <v>448</v>
+        <v>780</v>
       </c>
       <c r="H20" t="n">
-        <v>2.89</v>
+        <v>23.65</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>14960</v>
+        <v>91700</v>
       </c>
       <c r="K20" t="n">
-        <v>15040</v>
+        <v>90000</v>
       </c>
       <c r="L20" t="n">
-        <v>15040</v>
+        <v>90700</v>
       </c>
       <c r="M20" t="n">
-        <v>14190</v>
+        <v>87800</v>
       </c>
       <c r="N20" t="n">
-        <v>1.55</v>
+        <v>23.61</v>
       </c>
       <c r="O20" t="n">
-        <v>79334497050</v>
+        <v>139316464900</v>
       </c>
       <c r="P20" t="n">
-        <v>31500</v>
+        <v>139200</v>
       </c>
       <c r="Q20" t="n">
-        <v>1263</v>
+        <v>57000</v>
       </c>
       <c r="R20" t="n">
-        <v>-492000</v>
+        <v>-273000</v>
       </c>
       <c r="S20" t="n">
-        <v>-7000</v>
+        <v>31000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>미국 광통신 관련주로 분류되며, 외인 매수세 유입 및 AI 관련주로서의 기대감이 형성되고 있음. 다만, 주가 변동성이 관찰됨.</t>
+          <t>미국 원전 건설 '팀코리아' 및 웨스턴하우스 지분 인수 가능성, 역사적 호재 언급.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '외인']</t>
+          <t>['원전', '웨스턴하우스', '호재']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14960</v>
+        <v>15070</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-4.35%</t>
+          <t>-3.64%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F21" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G21" t="n">
-        <v>364</v>
+        <v>391</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2358,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>22550178915</v>
+        <v>22963001215</v>
       </c>
       <c r="P21" t="n">
         <v>19380</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>LH 발주 반도체 설계 용역 수주 및 킨텍스 공시 등 실질적인 수주 내용이 언급되며, 긍정적인 전망이 나오고 있음. 수주잔고 및 흑자 전환 가능성에 대한 기대가 존재함.</t>
+          <t>킨텍스 수주 공시 및 흑자 전환 기대감. 14800원 추가 매수 의견 및 역대 최대 수주 잔고.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['수주', '공시', '건설']</t>
+          <t>['수주', '킨텍스', '흑자']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2403,162 +2403,162 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29550</v>
+        <v>14340</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-4.98%</t>
+          <t>-4.14%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.17</v>
+        <v>1.34</v>
       </c>
       <c r="E22" t="n">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="F22" t="n">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="G22" t="n">
-        <v>122</v>
+        <v>450</v>
       </c>
       <c r="H22" t="n">
-        <v>12.31</v>
+        <v>2.89</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>31100</v>
+        <v>14960</v>
       </c>
       <c r="K22" t="n">
-        <v>30450</v>
+        <v>15040</v>
       </c>
       <c r="L22" t="n">
-        <v>30600</v>
+        <v>15040</v>
       </c>
       <c r="M22" t="n">
-        <v>28800</v>
+        <v>14190</v>
       </c>
       <c r="N22" t="n">
-        <v>12.14</v>
+        <v>1.55</v>
       </c>
       <c r="O22" t="n">
-        <v>52863268750</v>
+        <v>81343334755</v>
       </c>
       <c r="P22" t="n">
-        <v>75900</v>
+        <v>31500</v>
       </c>
       <c r="Q22" t="n">
-        <v>15000</v>
+        <v>1263</v>
       </c>
       <c r="R22" t="n">
-        <v>-343000</v>
+        <v>-492000</v>
       </c>
       <c r="S22" t="n">
-        <v>1000</v>
+        <v>-7000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>차익실현 매물 출회 및 급락 마감. 가온전선과의 비교 속 단기 변동성 확대.</t>
+          <t>미국 광통신 관련주로 분류되며, 외인 매수세 유입 및 AI 관련주로서의 기대감이 형성되고 있음. 다만, 주가 변동성이 관찰됨.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['차익실현', '급락', '단기변동성']</t>
+          <t>['광통신', 'AI', '외인']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3650</v>
+        <v>29550</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-5.56%</t>
+          <t>-4.98%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.54</v>
+        <v>0.17</v>
       </c>
       <c r="E23" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F23" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G23" t="n">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="H23" t="n">
-        <v>1.54</v>
+        <v>12.31</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>3865</v>
+        <v>31100</v>
       </c>
       <c r="K23" t="n">
-        <v>3845</v>
+        <v>30450</v>
       </c>
       <c r="L23" t="n">
-        <v>4075</v>
+        <v>30600</v>
       </c>
       <c r="M23" t="n">
-        <v>3605</v>
+        <v>28800</v>
       </c>
       <c r="N23" t="n">
-        <v>2.08</v>
+        <v>12.14</v>
       </c>
       <c r="O23" t="n">
-        <v>47443026018</v>
+        <v>53645215325</v>
       </c>
       <c r="P23" t="n">
-        <v>4335</v>
+        <v>75900</v>
       </c>
       <c r="Q23" t="n">
-        <v>1246</v>
+        <v>15000</v>
       </c>
       <c r="R23" t="n">
-        <v>-210000</v>
+        <v>-343000</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>최근 하락세 속 조정 및 반등에 대한 엇갈린 전망. 일부 매수 의견과 차트 붕괴 경고.</t>
+          <t>차익실현 매물 출회 및 급락 마감. 가온전선과의 비교 속 단기 변동성 확대.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,11 +2567,11 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['조정', '나락', '분할매수']</t>
+          <t>['차익실현', '급락', '단기변동성']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,182 +2580,182 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2115</v>
+        <v>3645</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-6.42%</t>
+          <t>-5.69%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.35</v>
+        <v>-0.54</v>
       </c>
       <c r="E24" t="n">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="F24" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G24" t="n">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="H24" t="n">
-        <v>4.91</v>
+        <v>1.54</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>2260</v>
+        <v>3865</v>
       </c>
       <c r="K24" t="n">
-        <v>2250</v>
+        <v>3845</v>
       </c>
       <c r="L24" t="n">
-        <v>2290</v>
+        <v>4075</v>
       </c>
       <c r="M24" t="n">
-        <v>2080</v>
+        <v>3605</v>
       </c>
       <c r="N24" t="n">
-        <v>5.26</v>
+        <v>2.08</v>
       </c>
       <c r="O24" t="n">
-        <v>6024412892</v>
+        <v>47760210766</v>
       </c>
       <c r="P24" t="n">
-        <v>2705</v>
+        <v>4335</v>
       </c>
       <c r="Q24" t="n">
-        <v>1418</v>
+        <v>1246</v>
       </c>
       <c r="R24" t="n">
-        <v>-133000</v>
+        <v>-210000</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>M&amp;A 관련 이슈로 인한 변동성 확대, 적대적 M&amp;A 가능성 및 신주인수 영향.</t>
+          <t>최근 하락세 속 조정 및 반등에 대한 엇갈린 전망. 일부 매수 의견과 차트 붕괴 경고.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['M&amp;A', '신주인수', '변동성']</t>
+          <t>['조정', '나락', '분할매수']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>삼미금속</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>12130</v>
+        <v>2110</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-6.91%</t>
+          <t>-6.64%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.22</v>
+        <v>-0.35</v>
       </c>
       <c r="E25" t="n">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F25" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="G25" t="n">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="H25" t="n">
-        <v>0.14</v>
+        <v>4.91</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>13030</v>
+        <v>2260</v>
       </c>
       <c r="K25" t="n">
-        <v>13160</v>
+        <v>2250</v>
       </c>
       <c r="L25" t="n">
-        <v>13240</v>
+        <v>2290</v>
       </c>
       <c r="M25" t="n">
-        <v>12010</v>
+        <v>2080</v>
       </c>
       <c r="N25" t="n">
-        <v>0.36</v>
+        <v>5.26</v>
       </c>
       <c r="O25" t="n">
-        <v>62682643290</v>
+        <v>6071182840</v>
       </c>
       <c r="P25" t="n">
-        <v>20850</v>
+        <v>2705</v>
       </c>
       <c r="Q25" t="n">
-        <v>4020</v>
+        <v>1418</v>
       </c>
       <c r="R25" t="n">
-        <v>25000</v>
+        <v>-133000</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>그래핀 신소재 관련 언급과 함께 최대 호재 가능성이 제기되나, 구체적인 공시나 뉴스가 부족하여 기대감 위주의 논의가 진행됨.</t>
+          <t>M&amp;A 관련 이슈로 인한 변동성 확대, 적대적 M&amp;A 가능성 및 신주인수 영향.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['그래핀', '신소재', '호재']</t>
+          <t>['M&amp;A', '신주인수', '변동성']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2764,38 +2764,38 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>012210</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>27950</v>
+        <v>12155</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-7.76%</t>
+          <t>-6.72%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.02</v>
+        <v>-0.22</v>
       </c>
       <c r="E26" t="n">
-        <v>215</v>
+        <v>90</v>
       </c>
       <c r="F26" t="n">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="G26" t="n">
-        <v>354</v>
+        <v>87</v>
       </c>
       <c r="H26" t="n">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2803,51 +2803,51 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>30300</v>
+        <v>13030</v>
       </c>
       <c r="K26" t="n">
-        <v>30800</v>
+        <v>13160</v>
       </c>
       <c r="L26" t="n">
-        <v>31500</v>
+        <v>13240</v>
       </c>
       <c r="M26" t="n">
-        <v>27750</v>
+        <v>12010</v>
       </c>
       <c r="N26" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="O26" t="n">
-        <v>117889605300</v>
+        <v>63346250475</v>
       </c>
       <c r="P26" t="n">
-        <v>39350</v>
+        <v>20850</v>
       </c>
       <c r="Q26" t="n">
-        <v>8200</v>
+        <v>4020</v>
       </c>
       <c r="R26" t="n">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="S26" t="n">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>좋은 재료 대비 낮은 주가 상승률에 대한 불만 표출. 주포 이탈 및 계단식 하락 가능성 제기. 33000원 이상 고가 매수자들의 손실 우려.</t>
+          <t>그래핀 신소재 관련 호재 및 3500억 달러 투자 기대감. 20% 만족 후 이탈 의견.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['하락', '주포이탈', '고가매수']</t>
+          <t>['그래핀', '호재', '투자']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -2856,38 +2856,38 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>원풍물산</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>137</v>
+        <v>27950</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-44.76%</t>
+          <t>-7.76%</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-0.32</v>
+        <v>0.02</v>
       </c>
       <c r="E27" t="n">
-        <v>71</v>
+        <v>216</v>
       </c>
       <c r="F27" t="n">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="G27" t="n">
-        <v>113</v>
+        <v>356</v>
       </c>
       <c r="H27" t="n">
-        <v>5.86</v>
+        <v>0.33</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2895,58 +2895,150 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>248</v>
+        <v>30300</v>
       </c>
       <c r="K27" t="n">
-        <v>172</v>
+        <v>30800</v>
       </c>
       <c r="L27" t="n">
-        <v>172</v>
+        <v>31500</v>
       </c>
       <c r="M27" t="n">
-        <v>137</v>
+        <v>27750</v>
       </c>
       <c r="N27" t="n">
-        <v>6.18</v>
+        <v>0.31</v>
       </c>
       <c r="O27" t="n">
-        <v>837239701</v>
+        <v>118853995725</v>
       </c>
       <c r="P27" t="n">
-        <v>901</v>
+        <v>39350</v>
       </c>
       <c r="Q27" t="n">
-        <v>137</v>
+        <v>8200</v>
       </c>
       <c r="R27" t="n">
-        <v>25000</v>
+        <v>12000</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>원풍물산, 시가총액 미달 상폐 우려 속에서 허매수/허매도 동향 관찰. 거래량은 많으나 실제 주가 상승 동력은 부족.</t>
+          <t>상승세 둔화 및 급락 우려 제기. 35000원 이상 물린 투자자 손절 권고.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
+          <t>['급락', '손절', '주포']</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>386380</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>원풍물산</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>137</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>-44.76%</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="E28" t="n">
+        <v>74</v>
+      </c>
+      <c r="F28" t="n">
+        <v>41</v>
+      </c>
+      <c r="G28" t="n">
+        <v>117</v>
+      </c>
+      <c r="H28" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>248</v>
+      </c>
+      <c r="K28" t="n">
+        <v>172</v>
+      </c>
+      <c r="L28" t="n">
+        <v>172</v>
+      </c>
+      <c r="M28" t="n">
+        <v>137</v>
+      </c>
+      <c r="N28" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="O28" t="n">
+        <v>837239701</v>
+      </c>
+      <c r="P28" t="n">
+        <v>901</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>137</v>
+      </c>
+      <c r="R28" t="n">
+        <v>25000</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>원풍물산, 시가총액 미달 상폐 우려 속에서 허매수/허매도 동향 관찰. 거래량은 많으나 실제 주가 상승 동력은 부족.</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
           <t>['상폐', '시가총액', '허매수']</t>
         </is>
       </c>
-      <c r="X27" t="n">
+      <c r="X28" t="n">
         <v>2</v>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>추적</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>008290</t>
         </is>

--- a/data/trending_integrated_20260910_12.xlsx
+++ b/data/trending_integrated_20260910_12.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4185</v>
+        <v>3945</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+109.25%</t>
+          <t>+97.25%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="F2" t="n">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="G2" t="n">
-        <v>381</v>
+        <v>403</v>
       </c>
       <c r="H2" t="n">
         <v>3.2</v>
@@ -604,19 +604,19 @@
         <v>5700</v>
       </c>
       <c r="M2" t="n">
-        <v>4000</v>
+        <v>3780</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>652408874139</v>
+        <v>669296676682</v>
       </c>
       <c r="P2" t="n">
         <v>5700</v>
       </c>
       <c r="Q2" t="n">
-        <v>4000</v>
+        <v>3780</v>
       </c>
       <c r="R2" t="n">
         <v>-149000</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29275</v>
+        <v>29400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+26.19%</t>
+          <t>+26.72%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G3" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H3" t="n">
         <v>7.54</v>
@@ -702,7 +702,7 @@
         <v>7.58</v>
       </c>
       <c r="O3" t="n">
-        <v>43796798325</v>
+        <v>44316781025</v>
       </c>
       <c r="P3" t="n">
         <v>34750</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14740</v>
+        <v>14630</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+21.92%</t>
+          <t>+21.01%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.03</v>
       </c>
       <c r="E4" t="n">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="F4" t="n">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="G4" t="n">
-        <v>427</v>
+        <v>410</v>
       </c>
       <c r="H4" t="n">
         <v>0.03</v>
@@ -794,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>276846328175</v>
+        <v>282608686940</v>
       </c>
       <c r="P4" t="n">
         <v>36200</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>이란발 지정학적 리스크 및 유가 급등 전망. WTI 110달러 돌파 및 급등 예상.</t>
+          <t>지정학적 리스크로 인한 유가 급등 전망과 함께 단기 급등 및 상한가 마감에 대한 기대감이 매우 높음.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['유가', '이란', '호르무즈']</t>
+          <t>['유가', '호르무즈']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3645</v>
+        <v>3570</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+17.39%</t>
+          <t>+14.98%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>23755545846</v>
+        <v>23967159050</v>
       </c>
       <c r="P5" t="n">
         <v>20800</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13100</v>
+        <v>12960</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+13.42%</t>
+          <t>+12.21%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.26</v>
       </c>
       <c r="E6" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H6" t="n">
         <v>4.37</v>
@@ -978,7 +978,7 @@
         <v>4.63</v>
       </c>
       <c r="O6" t="n">
-        <v>94251190435</v>
+        <v>94991919840</v>
       </c>
       <c r="P6" t="n">
         <v>33575</v>
@@ -1023,184 +1023,184 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>카프로</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8340</v>
+        <v>164</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+12.40%</t>
+          <t>+11.56%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.4</v>
+        <v>-0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>249</v>
+        <v>57</v>
       </c>
       <c r="F7" t="n">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="G7" t="n">
-        <v>1297</v>
+        <v>50</v>
       </c>
       <c r="H7" t="n">
-        <v>1.17</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>7420</v>
+        <v>147</v>
       </c>
       <c r="K7" t="n">
-        <v>8000</v>
+        <v>181</v>
       </c>
       <c r="L7" t="n">
-        <v>9100</v>
+        <v>260</v>
       </c>
       <c r="M7" t="n">
-        <v>7930</v>
+        <v>164</v>
       </c>
       <c r="N7" t="n">
-        <v>0.77</v>
+        <v>0.08</v>
       </c>
       <c r="O7" t="n">
-        <v>64611309745</v>
+        <v>632864490</v>
       </c>
       <c r="P7" t="n">
-        <v>21500</v>
+        <v>3660</v>
       </c>
       <c r="Q7" t="n">
-        <v>2300</v>
+        <v>133</v>
       </c>
       <c r="R7" t="n">
-        <v>117000</v>
+        <v>-18000</v>
       </c>
       <c r="S7" t="n">
-        <v>-8000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>글로벌 제약사와의 임상 참여 및 기술 이전 기대감으로 인한 급등 전망.</t>
+          <t>거래량 급증하며 60% 이상 급등. 회생 및 상장 기대감 속 추격매수 의견.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['임상', '기술 이전', 'FDA']</t>
+          <t>['급등', '거래량', '회생']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>006380</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>카프로</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>164</v>
+        <v>8210</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+11.56%</t>
+          <t>+10.65%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.01</v>
+        <v>0.4</v>
       </c>
       <c r="E8" t="n">
-        <v>56</v>
+        <v>257</v>
       </c>
       <c r="F8" t="n">
-        <v>36</v>
+        <v>114</v>
       </c>
       <c r="G8" t="n">
-        <v>49</v>
+        <v>1347</v>
       </c>
       <c r="H8" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.17</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>147</v>
+        <v>7420</v>
       </c>
       <c r="K8" t="n">
-        <v>181</v>
+        <v>8000</v>
       </c>
       <c r="L8" t="n">
-        <v>260</v>
+        <v>9100</v>
       </c>
       <c r="M8" t="n">
-        <v>164</v>
+        <v>7930</v>
       </c>
       <c r="N8" t="n">
-        <v>0.08</v>
+        <v>0.77</v>
       </c>
       <c r="O8" t="n">
-        <v>632864490</v>
+        <v>65256252595</v>
       </c>
       <c r="P8" t="n">
-        <v>3660</v>
+        <v>21500</v>
       </c>
       <c r="Q8" t="n">
-        <v>133</v>
+        <v>2300</v>
       </c>
       <c r="R8" t="n">
-        <v>-18000</v>
+        <v>117000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-8000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>거래량 급증하며 60% 이상 급등. 회생 및 상장 기대감 속 추격매수 의견.</t>
+          <t>폐암 학회 발표 및 글로벌 제약사와의 협력 가능성을 바탕으로 강력한 상승 재료와 10배 이상 상승 전망을 제시함.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['급등', '거래량', '회생']</t>
+          <t>['폐암', '학회', '다락손라십']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>006380</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1934</v>
+        <v>1926</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+9.89%</t>
+          <t>+9.43%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>133</v>
       </c>
       <c r="F9" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G9" t="n">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H9" t="n">
         <v>2.12</v>
@@ -1254,7 +1254,7 @@
         <v>2.07</v>
       </c>
       <c r="O9" t="n">
-        <v>184843220372</v>
+        <v>186463058613</v>
       </c>
       <c r="P9" t="n">
         <v>4795</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>외인 매수세 유입 속 주가 급등락 반복. 120일선 돌파 기대감과 급락 우려 상존.</t>
+          <t>감정적인 언급과 개인적인 경험에 기반한 투자 의견이 주를 이루며, 객관적인 사실 기반 분석은 부족함.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['외인', '급등락', '120일선']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14430</v>
+        <v>14390</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+8.41%</t>
+          <t>+8.11%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.53</v>
       </c>
       <c r="E10" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F10" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G10" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="H10" t="n">
         <v>0.57</v>
@@ -1346,7 +1346,7 @@
         <v>1.1</v>
       </c>
       <c r="O10" t="n">
-        <v>112564301955</v>
+        <v>113883448515</v>
       </c>
       <c r="P10" t="n">
         <v>23000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>중동 강관 수출 기대감 속 주가 상승. 재무제표 기반 3만원 이상 목표치 제시.</t>
+          <t>주가 상승에 대한 기대감이 있으나, 중동 관련 사업과의 연관성에 대한 혼란과 확인되지 않은 정보가 혼재함.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['중동', '강관', '재무제표']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,21 +1395,21 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+1.97%</t>
+          <t>+2.56%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.38</v>
       </c>
       <c r="E11" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G11" t="n">
         <v>60</v>
@@ -1438,7 +1438,7 @@
         <v>2.42</v>
       </c>
       <c r="O11" t="n">
-        <v>8102885494</v>
+        <v>8137274785</v>
       </c>
       <c r="P11" t="n">
         <v>2610</v>
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3885</v>
+        <v>2120</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+1.97%</t>
+          <t>+1.68%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-1.62</v>
+        <v>0.34</v>
       </c>
       <c r="E12" t="n">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="F12" t="n">
         <v>55</v>
       </c>
       <c r="G12" t="n">
-        <v>168</v>
+        <v>226</v>
       </c>
       <c r="H12" t="n">
-        <v>1.57</v>
+        <v>0.85</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,47 +1515,47 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>3810</v>
+        <v>2085</v>
       </c>
       <c r="K12" t="n">
-        <v>3870</v>
+        <v>2255</v>
       </c>
       <c r="L12" t="n">
-        <v>4250</v>
+        <v>2395</v>
       </c>
       <c r="M12" t="n">
-        <v>3660</v>
+        <v>2040</v>
       </c>
       <c r="N12" t="n">
-        <v>3.19</v>
+        <v>0.51</v>
       </c>
       <c r="O12" t="n">
-        <v>133785053743</v>
+        <v>19307662803</v>
       </c>
       <c r="P12" t="n">
-        <v>8100</v>
+        <v>2930</v>
       </c>
       <c r="Q12" t="n">
-        <v>592</v>
+        <v>910</v>
       </c>
       <c r="R12" t="n">
-        <v>-540000</v>
+        <v>-175000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>투기과열종목 지정 회피 및 6G 통신 테마 기대감. 15% 상승 전망 및 10버거 목표 제시.</t>
+          <t>매집 및 수혜 기대감이 있으나, 구체적인 근거 제시 없이 개인적인 투자 판단에 의존하는 경향이 강함.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['투기과열', '6G', '통신']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2105</v>
+        <v>155800</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>+1.50%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.34</v>
+        <v>0.4</v>
       </c>
       <c r="E13" t="n">
-        <v>122</v>
+        <v>391</v>
       </c>
       <c r="F13" t="n">
-        <v>54</v>
+        <v>181</v>
       </c>
       <c r="G13" t="n">
-        <v>212</v>
+        <v>972</v>
       </c>
       <c r="H13" t="n">
-        <v>0.85</v>
+        <v>15.65</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>2085</v>
+        <v>153500</v>
       </c>
       <c r="K13" t="n">
-        <v>2255</v>
+        <v>155500</v>
       </c>
       <c r="L13" t="n">
-        <v>2395</v>
+        <v>164700</v>
       </c>
       <c r="M13" t="n">
-        <v>2040</v>
+        <v>150200</v>
       </c>
       <c r="N13" t="n">
-        <v>0.51</v>
+        <v>15.25</v>
       </c>
       <c r="O13" t="n">
-        <v>19163103298</v>
+        <v>354867137450</v>
       </c>
       <c r="P13" t="n">
-        <v>2930</v>
+        <v>164700</v>
       </c>
       <c r="Q13" t="n">
-        <v>910</v>
+        <v>87700</v>
       </c>
       <c r="R13" t="n">
-        <v>-175000</v>
+        <v>104000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>새만금 및 LH 관련 사업 기대감 속에서 매집 움직임 포착, 주가 상승 가능성.</t>
+          <t>유가 상승에 따른 긍정적 전망과 함께 매수 기회라는 의견이 제시되나, 단기적인 상승에 대한 경계도 존재함.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['새만금', 'LH', '매집']</t>
+          <t>['유가', '매수']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>096770</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>154300</v>
+        <v>3860</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+0.52%</t>
+          <t>+1.31%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.4</v>
+        <v>-1.62</v>
       </c>
       <c r="E14" t="n">
-        <v>377</v>
+        <v>85</v>
       </c>
       <c r="F14" t="n">
-        <v>176</v>
+        <v>55</v>
       </c>
       <c r="G14" t="n">
-        <v>951</v>
+        <v>168</v>
       </c>
       <c r="H14" t="n">
-        <v>15.65</v>
+        <v>1.57</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>153500</v>
+        <v>3810</v>
       </c>
       <c r="K14" t="n">
-        <v>155500</v>
+        <v>3870</v>
       </c>
       <c r="L14" t="n">
-        <v>164700</v>
+        <v>4250</v>
       </c>
       <c r="M14" t="n">
-        <v>150200</v>
+        <v>3660</v>
       </c>
       <c r="N14" t="n">
-        <v>15.25</v>
+        <v>3.19</v>
       </c>
       <c r="O14" t="n">
-        <v>342328455550</v>
+        <v>134718295682</v>
       </c>
       <c r="P14" t="n">
-        <v>164700</v>
+        <v>8100</v>
       </c>
       <c r="Q14" t="n">
-        <v>87700</v>
+        <v>592</v>
       </c>
       <c r="R14" t="n">
-        <v>104000</v>
+        <v>-540000</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>유가 상승으로 인한 SK이노베이션 주가 상승 기대감, 투자 심리 긍정적.</t>
+          <t>투자경고 종목 지정 회피와 6G 테마에 대한 기대감으로 상승 전망이 있으나, 주가 변동성에 대한 우려도 있음.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['유가상승', '주가상승', '투자심리']</t>
+          <t>['6G', '광통신']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1844000</v>
+        <v>6850</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.65%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.01</v>
+        <v>-1.03</v>
       </c>
       <c r="E15" t="n">
-        <v>799</v>
+        <v>114</v>
       </c>
       <c r="F15" t="n">
-        <v>471</v>
+        <v>60</v>
       </c>
       <c r="G15" t="n">
-        <v>1938</v>
+        <v>305</v>
       </c>
       <c r="H15" t="n">
-        <v>50.67</v>
+        <v>15.68</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1856000</v>
+        <v>6860</v>
       </c>
       <c r="K15" t="n">
-        <v>1879000</v>
+        <v>6800</v>
       </c>
       <c r="L15" t="n">
-        <v>1890000</v>
+        <v>6850</v>
       </c>
       <c r="M15" t="n">
-        <v>1811000</v>
+        <v>6400</v>
       </c>
       <c r="N15" t="n">
-        <v>50.66</v>
+        <v>16.71</v>
       </c>
       <c r="O15" t="n">
-        <v>3616217989500</v>
+        <v>12418795855</v>
       </c>
       <c r="P15" t="n">
-        <v>2987000</v>
+        <v>13000</v>
       </c>
       <c r="Q15" t="n">
-        <v>293000</v>
+        <v>6030</v>
       </c>
       <c r="R15" t="n">
-        <v>-110000</v>
+        <v>-273000</v>
       </c>
       <c r="S15" t="n">
-        <v>-78000</v>
+        <v>-10000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>SK하이닉스 주가 상승 추세, 대규모 자사주 매입 및 리밸런싱 효과 기대.</t>
+          <t>외국인 매도세 및 분사 관련 불확실성 속 기관의 관망세. 주가 조작 및 패턴 반복에 대한 불만 제기.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['주가상승', '자사주매입', '리밸런싱']</t>
+          <t>['외국인', '기관', '분사']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>267250</v>
+        <v>267750</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.83%</t>
+          <t>-0.65%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.04</v>
       </c>
       <c r="E16" t="n">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="F16" t="n">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="G16" t="n">
-        <v>1272</v>
+        <v>1289</v>
       </c>
       <c r="H16" t="n">
         <v>46.81</v>
@@ -1898,7 +1898,7 @@
         <v>46.85</v>
       </c>
       <c r="O16" t="n">
-        <v>2121469276000</v>
+        <v>2168604479500</v>
       </c>
       <c r="P16" t="n">
         <v>374500</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>하이닉스 대비 상승세 미미. 악재 누적 및 매도 의견 우세 속 주가 하락 전망.</t>
+          <t>하락세에 대한 우려와 매도 의견이 다수 존재하며, 일부 긍정적인 전망도 있으나 근거는 부족함.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['하이닉스', '매도', '악재']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1943,83 +1943,83 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14100</v>
+        <v>1843000</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.54%</t>
+          <t>-0.70%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.45</v>
+        <v>0.01</v>
       </c>
       <c r="E17" t="n">
-        <v>103</v>
+        <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>64</v>
+        <v>472</v>
       </c>
       <c r="G17" t="n">
-        <v>590</v>
+        <v>1969</v>
       </c>
       <c r="H17" t="n">
-        <v>6.09</v>
+        <v>50.67</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>14320</v>
+        <v>1856000</v>
       </c>
       <c r="K17" t="n">
-        <v>13800</v>
+        <v>1879000</v>
       </c>
       <c r="L17" t="n">
-        <v>14400</v>
+        <v>1890000</v>
       </c>
       <c r="M17" t="n">
-        <v>13260</v>
+        <v>1811000</v>
       </c>
       <c r="N17" t="n">
-        <v>5.64</v>
+        <v>50.66</v>
       </c>
       <c r="O17" t="n">
-        <v>126346035695</v>
+        <v>3713589868500</v>
       </c>
       <c r="P17" t="n">
-        <v>30200</v>
+        <v>2987000</v>
       </c>
       <c r="Q17" t="n">
-        <v>3540</v>
+        <v>293000</v>
       </c>
       <c r="R17" t="n">
-        <v>-132000</v>
+        <v>-110000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-78000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 신규 원전 건설 및 공매도 금지 이슈로 우리기술 주가 상승 기대감.</t>
+          <t>대세 상승에 대한 확신과 긍정적인 종가 전망이 우세하나, 특정 기관의 매도 언급 등 일부 부정적인 의견도 혼재함.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['원전주', '공매도금지', '주가상승']</t>
+          <t>['대세 상승', '폭등']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,77 +2028,77 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>19010</v>
+        <v>14030</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.26%</t>
+          <t>-2.03%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.21</v>
+        <v>0.45</v>
       </c>
       <c r="E18" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F18" t="n">
         <v>64</v>
       </c>
       <c r="G18" t="n">
-        <v>359</v>
+        <v>609</v>
       </c>
       <c r="H18" t="n">
-        <v>10.64</v>
+        <v>6.09</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>19450</v>
+        <v>14320</v>
       </c>
       <c r="K18" t="n">
-        <v>18900</v>
+        <v>13800</v>
       </c>
       <c r="L18" t="n">
-        <v>19220</v>
+        <v>14400</v>
       </c>
       <c r="M18" t="n">
-        <v>18670</v>
+        <v>13260</v>
       </c>
       <c r="N18" t="n">
-        <v>10.85</v>
+        <v>5.64</v>
       </c>
       <c r="O18" t="n">
-        <v>76155136965</v>
+        <v>127565181645</v>
       </c>
       <c r="P18" t="n">
-        <v>40350</v>
+        <v>30200</v>
       </c>
       <c r="Q18" t="n">
-        <v>3320</v>
+        <v>3540</v>
       </c>
       <c r="R18" t="n">
-        <v>-67000</v>
+        <v>-132000</v>
       </c>
       <c r="S18" t="n">
-        <v>-52000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 투자 기대감과 대차해지 운동 동참 호소. 주주들의 적극적인 참여 독려.</t>
+          <t>원전 관련 긍정적인 뉴스 및 정책 기대를 바탕으로 강한 상승 전망과 함께 공매도 세력에 대한 비판이 제기됨.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['미국 투자', '대차해지', '주주']</t>
+          <t>['원전', '공매도']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6670</v>
+        <v>18980</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.77%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-1.03</v>
+        <v>-0.21</v>
       </c>
       <c r="E19" t="n">
         <v>108</v>
       </c>
       <c r="F19" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G19" t="n">
-        <v>304</v>
+        <v>366</v>
       </c>
       <c r="H19" t="n">
-        <v>15.68</v>
+        <v>10.64</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,51 +2159,51 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>6860</v>
+        <v>19450</v>
       </c>
       <c r="K19" t="n">
-        <v>6800</v>
+        <v>18900</v>
       </c>
       <c r="L19" t="n">
-        <v>6820</v>
+        <v>19220</v>
       </c>
       <c r="M19" t="n">
-        <v>6400</v>
+        <v>18670</v>
       </c>
       <c r="N19" t="n">
-        <v>16.71</v>
+        <v>10.85</v>
       </c>
       <c r="O19" t="n">
-        <v>11641052955</v>
+        <v>78150673635</v>
       </c>
       <c r="P19" t="n">
-        <v>13000</v>
+        <v>40350</v>
       </c>
       <c r="Q19" t="n">
-        <v>6030</v>
+        <v>3320</v>
       </c>
       <c r="R19" t="n">
-        <v>-273000</v>
+        <v>-67000</v>
       </c>
       <c r="S19" t="n">
-        <v>-10000</v>
+        <v>-52000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>외국인 매도세 및 분사 관련 불확실성 속 기관의 관망세. 주가 조작 및 패턴 반복에 대한 불만 제기.</t>
+          <t>미국 투자 기대감과 대차해지 운동 동참 호소. 주주들의 적극적인 참여 독려.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['외국인', '기관', '분사']</t>
+          <t>['미국 투자', '대차해지', '주주']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>88800</v>
+        <v>88900</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.16%</t>
+          <t>-3.05%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.04</v>
       </c>
       <c r="E20" t="n">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F20" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G20" t="n">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="H20" t="n">
         <v>23.65</v>
@@ -2266,7 +2266,7 @@
         <v>23.61</v>
       </c>
       <c r="O20" t="n">
-        <v>139316464900</v>
+        <v>141831423550</v>
       </c>
       <c r="P20" t="n">
         <v>139200</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15070</v>
+        <v>15120</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.64%</t>
+          <t>-3.32%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F21" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G21" t="n">
-        <v>391</v>
+        <v>423</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2358,7 +2358,7 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>22963001215</v>
+        <v>23732671295</v>
       </c>
       <c r="P21" t="n">
         <v>19380</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>킨텍스 수주 공시 및 흑자 전환 기대감. 14800원 추가 매수 의견 및 역대 최대 수주 잔고.</t>
+          <t>호남 반도체 설계용역 발주 및 수주 공시 확인. 수주 잔고 증가에 따른 긍정적 전망 제시.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['수주', '킨텍스', '흑자']</t>
+          <t>['수주', '건설', '반도체']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14340</v>
+        <v>14380</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-4.14%</t>
+          <t>-3.88%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>1.34</v>
       </c>
       <c r="E22" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F22" t="n">
         <v>72</v>
       </c>
       <c r="G22" t="n">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="H22" t="n">
         <v>2.89</v>
@@ -2450,7 +2450,7 @@
         <v>1.55</v>
       </c>
       <c r="O22" t="n">
-        <v>81343334755</v>
+        <v>82087936615</v>
       </c>
       <c r="P22" t="n">
         <v>31500</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>미국 광통신 관련주로 분류되며, 외인 매수세 유입 및 AI 관련주로서의 기대감이 형성되고 있음. 다만, 주가 변동성이 관찰됨.</t>
+          <t>미국 광통신 관련주로 분류되며, 외인 매수세 유입과 함께 상승 추세 전망. 시간 외 거래에서도 긍정적인 흐름 관찰.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '외인']</t>
+          <t>['광통신', '외국인', 'AI']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2495,31 +2495,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>써니전자</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>29550</v>
+        <v>2155</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-4.98%</t>
+          <t>-4.65%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.17</v>
+        <v>-0.35</v>
       </c>
       <c r="E23" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="F23" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G23" t="n">
-        <v>123</v>
+        <v>166</v>
       </c>
       <c r="H23" t="n">
-        <v>12.31</v>
+        <v>4.91</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,47 +2527,47 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>31100</v>
+        <v>2260</v>
       </c>
       <c r="K23" t="n">
-        <v>30450</v>
+        <v>2250</v>
       </c>
       <c r="L23" t="n">
-        <v>30600</v>
+        <v>2290</v>
       </c>
       <c r="M23" t="n">
-        <v>28800</v>
+        <v>2080</v>
       </c>
       <c r="N23" t="n">
-        <v>12.14</v>
+        <v>5.26</v>
       </c>
       <c r="O23" t="n">
-        <v>53645215325</v>
+        <v>6191366750</v>
       </c>
       <c r="P23" t="n">
-        <v>75900</v>
+        <v>2705</v>
       </c>
       <c r="Q23" t="n">
-        <v>15000</v>
+        <v>1418</v>
       </c>
       <c r="R23" t="n">
-        <v>-343000</v>
+        <v>-133000</v>
       </c>
       <c r="S23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>차익실현 매물 출회 및 급락 마감. 가온전선과의 비교 속 단기 변동성 확대.</t>
+          <t>M&amp;A 관련 이슈로 인한 변동성 확대, 적대적 M&amp;A 가능성 및 신주인수 영향.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['차익실현', '급락', '단기변동성']</t>
+          <t>['M&amp;A', '신주인수', '변동성']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2575,82 +2575,82 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>004770</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3645</v>
+        <v>29600</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-5.69%</t>
+          <t>-4.82%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.54</v>
+        <v>0.17</v>
       </c>
       <c r="E24" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F24" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G24" t="n">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="H24" t="n">
-        <v>1.54</v>
+        <v>12.31</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>3865</v>
+        <v>31100</v>
       </c>
       <c r="K24" t="n">
-        <v>3845</v>
+        <v>30450</v>
       </c>
       <c r="L24" t="n">
-        <v>4075</v>
+        <v>30600</v>
       </c>
       <c r="M24" t="n">
-        <v>3605</v>
+        <v>28800</v>
       </c>
       <c r="N24" t="n">
-        <v>2.08</v>
+        <v>12.14</v>
       </c>
       <c r="O24" t="n">
-        <v>47760210766</v>
+        <v>54403315075</v>
       </c>
       <c r="P24" t="n">
-        <v>4335</v>
+        <v>75900</v>
       </c>
       <c r="Q24" t="n">
-        <v>1246</v>
+        <v>15000</v>
       </c>
       <c r="R24" t="n">
-        <v>-210000</v>
+        <v>-343000</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>최근 하락세 속 조정 및 반등에 대한 엇갈린 전망. 일부 매수 의견과 차트 붕괴 경고.</t>
+          <t>차익실현 매물 출회 및 급락 마감. 가온전선과의 비교 속 단기 변동성 확대.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,11 +2659,11 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['조정', '나락', '분할매수']</t>
+          <t>['차익실현', '급락', '단기변동성']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,99 +2672,99 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>써니전자</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2110</v>
+        <v>3645</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-6.64%</t>
+          <t>-5.69%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.35</v>
+        <v>-0.54</v>
       </c>
       <c r="E25" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="F25" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G25" t="n">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="H25" t="n">
-        <v>4.91</v>
+        <v>1.54</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>2260</v>
+        <v>3865</v>
       </c>
       <c r="K25" t="n">
-        <v>2250</v>
+        <v>3845</v>
       </c>
       <c r="L25" t="n">
-        <v>2290</v>
+        <v>4075</v>
       </c>
       <c r="M25" t="n">
-        <v>2080</v>
+        <v>3605</v>
       </c>
       <c r="N25" t="n">
-        <v>5.26</v>
+        <v>2.08</v>
       </c>
       <c r="O25" t="n">
-        <v>6071182840</v>
+        <v>47986507646</v>
       </c>
       <c r="P25" t="n">
-        <v>2705</v>
+        <v>4335</v>
       </c>
       <c r="Q25" t="n">
-        <v>1418</v>
+        <v>1246</v>
       </c>
       <c r="R25" t="n">
-        <v>-133000</v>
+        <v>-210000</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>M&amp;A 관련 이슈로 인한 변동성 확대, 적대적 M&amp;A 가능성 및 신주인수 영향.</t>
+          <t>최근 하락세 속 조정 및 반등에 대한 엇갈린 전망. 일부 매수 의견과 차트 붕괴 경고.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['M&amp;A', '신주인수', '변동성']</t>
+          <t>['조정', '나락', '분할매수']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>004770</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>12155</v>
+        <v>12070</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-6.72%</t>
+          <t>-7.37%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>-0.22</v>
       </c>
       <c r="E26" t="n">
+        <v>94</v>
+      </c>
+      <c r="F26" t="n">
+        <v>58</v>
+      </c>
+      <c r="G26" t="n">
         <v>90</v>
-      </c>
-      <c r="F26" t="n">
-        <v>57</v>
-      </c>
-      <c r="G26" t="n">
-        <v>87</v>
       </c>
       <c r="H26" t="n">
         <v>0.14</v>
@@ -2818,7 +2818,7 @@
         <v>0.36</v>
       </c>
       <c r="O26" t="n">
-        <v>63346250475</v>
+        <v>63773352535</v>
       </c>
       <c r="P26" t="n">
         <v>20850</v>
@@ -2834,16 +2834,16 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>그래핀 신소재 관련 호재 및 3500억 달러 투자 기대감. 20% 만족 후 이탈 의견.</t>
+          <t>꿈의 신소재 그래핀 관련 호재 언급되나, 심리 게임 양상으로 변동성 확대. 원전 관련 부정적 언급도 존재.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['그래핀', '호재', '투자']</t>
+          <t>['그래핀', '신소재', '원전']</t>
         </is>
       </c>
       <c r="X26" t="n">
@@ -2878,13 +2878,13 @@
         <v>0.02</v>
       </c>
       <c r="E27" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F27" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G27" t="n">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="H27" t="n">
         <v>0.33</v>
@@ -2910,7 +2910,7 @@
         <v>0.31</v>
       </c>
       <c r="O27" t="n">
-        <v>118853995725</v>
+        <v>120350554675</v>
       </c>
       <c r="P27" t="n">
         <v>39350</v>
@@ -2926,16 +2926,16 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>상승세 둔화 및 급락 우려 제기. 35000원 이상 물린 투자자 손절 권고.</t>
+          <t>신규주 상승 가능성 언급되나, 프로그램 매매와 계단식 하락 패턴 관찰. 급락 및 매도 의견 다수.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>['급락', '손절', '주포']</t>
+          <t>['신규주', '급락', '프로그램']</t>
         </is>
       </c>
       <c r="X27" t="n">
@@ -2970,13 +2970,13 @@
         <v>-0.32</v>
       </c>
       <c r="E28" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F28" t="n">
         <v>41</v>
       </c>
       <c r="G28" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H28" t="n">
         <v>5.86</v>
